--- a/results.xlsx
+++ b/results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29909"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\__my_github\dhrystone_score\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{8BBDD84F-20CC-4D29-A4BF-71EC9BCBF77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BBE6C7F-579F-4AC6-9892-A5F54641EAAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="948" yWindow="-108" windowWidth="29880" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="840" yWindow="-108" windowWidth="29988" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="results" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="100">
   <si>
     <t>MCU</t>
   </si>
@@ -356,6 +356,30 @@
   </si>
   <si>
     <t>Os</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>STM32H523RET6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>O3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cortex-M33</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Os</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>STM32H523RET6(oc)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GD32H737VMT6(oc)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -714,7 +738,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P92"/>
+  <dimension ref="A1:P96"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.21875" style="1" bestFit="1" customWidth="1"/>
@@ -811,7 +835,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>91</v>
@@ -911,7 +935,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>93</v>
@@ -1009,109 +1033,109 @@
         <v>1.3531905933767816</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>7</v>
+        <v>95</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>49</v>
+        <v>96</v>
       </c>
       <c r="D12" s="1">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="E12" s="9">
-        <v>1.08</v>
-      </c>
-      <c r="F12" s="6">
+        <v>0.83199999999999996</v>
+      </c>
+      <c r="F12" s="7">
         <f>1000/E12/1.757</f>
-        <v>526.99255886506887</v>
+        <v>684.07687929600286</v>
       </c>
       <c r="G12" s="2">
         <f>F12/D12</f>
-        <v>1.3174813971626722</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1.5201708428800063</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="D13" s="1">
-        <v>368</v>
+        <v>400</v>
       </c>
       <c r="E13" s="9">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="F13" s="7">
+        <v>1.08</v>
+      </c>
+      <c r="F13" s="6">
         <f>1000/E13/1.757</f>
-        <v>494.91475093415164</v>
+        <v>526.99255886506887</v>
       </c>
       <c r="G13" s="2">
         <f>F13/D13</f>
-        <v>1.3448770405819339</v>
+        <v>1.3174813971626722</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="D14" s="1">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="E14" s="9">
-        <v>1.21</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="F14" s="7">
         <f>1000/E14/1.757</f>
-        <v>470.37352361510278</v>
+        <v>494.91475093415164</v>
       </c>
       <c r="G14" s="2">
         <f>F14/D14</f>
-        <v>1.3065931211530633</v>
+        <v>1.3448770405819339</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" s="1">
-        <v>320</v>
+        <v>360</v>
       </c>
       <c r="E15" s="9">
-        <v>1.232</v>
+        <v>1.21</v>
       </c>
       <c r="F15" s="7">
         <f>1000/E15/1.757</f>
-        <v>461.97399640769027</v>
+        <v>470.37352361510278</v>
       </c>
       <c r="G15" s="2">
         <f>F15/D15</f>
-        <v>1.4436687387740321</v>
+        <v>1.3065931211530633</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
@@ -1120,1300 +1144,1300 @@
         <v>50</v>
       </c>
       <c r="D16" s="1">
-        <v>272</v>
+        <v>320</v>
       </c>
       <c r="E16" s="9">
-        <v>1.4</v>
+        <v>1.232</v>
       </c>
       <c r="F16" s="7">
         <f>1000/E16/1.757</f>
-        <v>406.53711683876742</v>
+        <v>461.97399640769027</v>
       </c>
       <c r="G16" s="2">
         <f>F16/D16</f>
-        <v>1.4946217530837038</v>
+        <v>1.4436687387740321</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D17" s="1">
-        <v>192</v>
+        <v>272</v>
       </c>
       <c r="E17" s="9">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="F17" s="7">
         <f>1000/E17/1.757</f>
-        <v>381.98118360689551</v>
+        <v>406.53711683876742</v>
       </c>
       <c r="G17" s="2">
         <f>F17/D17</f>
-        <v>1.9894853312859142</v>
+        <v>1.4946217530837038</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="D18" s="1">
-        <v>288</v>
+        <v>250</v>
       </c>
       <c r="E18" s="9">
-        <v>1.54</v>
+        <v>1.464</v>
       </c>
       <c r="F18" s="7">
         <f>1000/E18/1.757</f>
-        <v>369.57919712615217</v>
+        <v>388.76500244144421</v>
       </c>
       <c r="G18" s="2">
         <f>F18/D18</f>
-        <v>1.2832611011324728</v>
+        <v>1.5550600097657767</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>12</v>
+        <v>98</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>7</v>
+        <v>97</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>50</v>
+        <v>96</v>
       </c>
       <c r="D19" s="1">
-        <v>240</v>
+        <v>450</v>
       </c>
       <c r="E19" s="9">
-        <v>1.59</v>
+        <v>1.4690000000000001</v>
       </c>
       <c r="F19" s="7">
         <f>1000/E19/1.757</f>
-        <v>357.95720979514107</v>
+        <v>387.44177234463876</v>
       </c>
       <c r="G19" s="2">
         <f>F19/D19</f>
-        <v>1.4914883741464211</v>
+        <v>0.86098171632141951</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>87</v>
+        <v>39</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>85</v>
+        <v>7</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>86</v>
+        <v>51</v>
       </c>
       <c r="D20" s="1">
-        <v>288</v>
+        <v>192</v>
       </c>
       <c r="E20" s="9">
-        <v>1.71</v>
+        <v>1.49</v>
       </c>
       <c r="F20" s="7">
         <f>1000/E20/1.757</f>
-        <v>332.83740559899087</v>
+        <v>381.98118360689551</v>
       </c>
       <c r="G20" s="2">
         <f>F20/D20</f>
-        <v>1.1556854361076072</v>
+        <v>1.9894853312859142</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="D21" s="1">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="E21" s="9">
-        <v>1.76</v>
+        <v>1.54</v>
       </c>
       <c r="F21" s="7">
         <f>1000/E21/1.757</f>
-        <v>323.38179748538312</v>
+        <v>369.57919712615217</v>
       </c>
       <c r="G21" s="2">
         <f>F21/D21</f>
-        <v>1.1549349910192255</v>
+        <v>1.2832611011324728</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D22" s="1">
-        <v>280</v>
+        <v>240</v>
       </c>
       <c r="E22" s="9">
-        <v>1.8</v>
+        <v>1.59</v>
       </c>
       <c r="F22" s="7">
         <f>1000/E22/1.757</f>
-        <v>316.19553531904131</v>
+        <v>357.95720979514107</v>
       </c>
       <c r="G22" s="2">
         <f>F22/D22</f>
-        <v>1.1292697689965761</v>
+        <v>1.4914883741464211</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>42</v>
+        <v>87</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>7</v>
+        <v>85</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="D23" s="1">
-        <v>240</v>
+        <v>288</v>
       </c>
       <c r="E23" s="9">
-        <v>1.8140000000000001</v>
+        <v>1.71</v>
       </c>
       <c r="F23" s="7">
         <f>1000/E23/1.757</f>
-        <v>313.7552169648701</v>
+        <v>332.83740559899087</v>
       </c>
       <c r="G23" s="2">
         <f>F23/D23</f>
-        <v>1.3073134040202921</v>
+        <v>1.1556854361076072</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="D24" s="1">
-        <v>208</v>
+        <v>280</v>
       </c>
       <c r="E24" s="9">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="F24" s="7">
         <f>1000/E24/1.757</f>
-        <v>307.64971004014831</v>
+        <v>323.38179748538312</v>
       </c>
       <c r="G24" s="2">
         <f>F24/D24</f>
-        <v>1.47908514442379</v>
+        <v>1.1549349910192255</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>84</v>
+        <v>14</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>85</v>
+        <v>7</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="D25" s="1">
-        <v>240</v>
+        <v>280</v>
       </c>
       <c r="E25" s="9">
-        <v>2.06</v>
+        <v>1.8</v>
       </c>
       <c r="F25" s="7">
         <f>1000/E25/1.757</f>
-        <v>276.28736095838559</v>
+        <v>316.19553531904131</v>
       </c>
       <c r="G25" s="2">
         <f>F25/D25</f>
-        <v>1.1511973373266067</v>
+        <v>1.1292697689965761</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="D26" s="1">
-        <v>368</v>
+        <v>240</v>
       </c>
       <c r="E26" s="9">
-        <v>2.0699999999999998</v>
+        <v>1.8140000000000001</v>
       </c>
       <c r="F26" s="7">
         <f>1000/E26/1.757</f>
-        <v>274.95263940786202</v>
+        <v>313.7552169648701</v>
       </c>
       <c r="G26" s="2">
         <f>F26/D26</f>
-        <v>0.74715391143440768</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1.3073134040202921</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="D27" s="1">
-        <v>256</v>
+        <v>208</v>
       </c>
       <c r="E27" s="9">
-        <v>2.12</v>
-      </c>
-      <c r="F27" s="6">
+        <v>1.85</v>
+      </c>
+      <c r="F27" s="7">
         <f>1000/E27/1.757</f>
-        <v>268.46790734635579</v>
+        <v>307.64971004014831</v>
       </c>
       <c r="G27" s="2">
         <f>F27/D27</f>
-        <v>1.0487027630717023</v>
+        <v>1.47908514442379</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
-        <v>15</v>
+        <v>84</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>7</v>
+        <v>85</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="D28" s="1">
-        <v>176</v>
+        <v>240</v>
       </c>
       <c r="E28" s="9">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="F28" s="7">
         <f>1000/E28/1.757</f>
-        <v>264.72184352291833</v>
+        <v>276.28736095838559</v>
       </c>
       <c r="G28" s="2">
         <f>F28/D28</f>
-        <v>1.5041013836529451</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1.1511973373266067</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="D29" s="1">
-        <v>200</v>
+        <v>368</v>
       </c>
       <c r="E29" s="9">
-        <v>2.16</v>
-      </c>
-      <c r="F29" s="6">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="F29" s="7">
         <f>1000/E29/1.757</f>
-        <v>263.49627943253444</v>
+        <v>274.95263940786202</v>
       </c>
       <c r="G29" s="2">
         <f>F29/D29</f>
-        <v>1.3174813971626722</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+        <v>0.74715391143440768</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>41</v>
+        <v>89</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="D30" s="1">
-        <v>180</v>
+        <v>256</v>
       </c>
       <c r="E30" s="9">
-        <v>2.1880000000000002</v>
-      </c>
-      <c r="F30" s="7">
+        <v>2.12</v>
+      </c>
+      <c r="F30" s="6">
         <f>1000/E30/1.757</f>
-        <v>260.12429779445807</v>
+        <v>268.46790734635579</v>
       </c>
       <c r="G30" s="2">
         <f>F30/D30</f>
-        <v>1.4451349877469892</v>
+        <v>1.0487027630717023</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D31" s="1">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E31" s="9">
-        <v>2.59</v>
+        <v>2.15</v>
       </c>
       <c r="F31" s="7">
         <f>1000/E31/1.757</f>
-        <v>219.74979288582023</v>
+        <v>264.72184352291833</v>
       </c>
       <c r="G31" s="2">
         <f>F31/D31</f>
-        <v>1.3080344814632157</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1.5041013836529451</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D32" s="1">
-        <v>108</v>
+        <v>200</v>
       </c>
       <c r="E32" s="9">
-        <v>2.66</v>
-      </c>
-      <c r="F32" s="7">
+        <v>2.16</v>
+      </c>
+      <c r="F32" s="6">
         <f>1000/E32/1.757</f>
-        <v>213.96690359935124</v>
+        <v>263.49627943253444</v>
       </c>
       <c r="G32" s="2">
         <f>F32/D32</f>
-        <v>1.9811750333273264</v>
+        <v>1.3174813971626722</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="D33" s="1">
-        <v>144</v>
+        <v>180</v>
       </c>
       <c r="E33" s="9">
-        <v>2.69</v>
+        <v>2.1880000000000002</v>
       </c>
       <c r="F33" s="7">
         <f>1000/E33/1.757</f>
-        <v>211.58065560381945</v>
+        <v>260.12429779445807</v>
       </c>
       <c r="G33" s="2">
         <f>F33/D33</f>
-        <v>1.4693101083598572</v>
+        <v>1.4451349877469892</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="D34" s="1">
-        <v>288</v>
+        <v>250</v>
       </c>
       <c r="E34" s="9">
-        <v>2.79</v>
-      </c>
-      <c r="F34" s="7">
+        <v>2.5870000000000002</v>
+      </c>
+      <c r="F34" s="3">
         <f>1000/E34/1.757</f>
-        <v>203.99711956067179</v>
+        <v>220.00462449720695</v>
       </c>
       <c r="G34" s="2">
         <f>F34/D34</f>
-        <v>0.7083233318078882</v>
+        <v>0.88001849798882781</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D35" s="1">
-        <v>192</v>
+        <v>168</v>
       </c>
       <c r="E35" s="9">
-        <v>2.82</v>
+        <v>2.59</v>
       </c>
       <c r="F35" s="7">
         <f>1000/E35/1.757</f>
-        <v>201.82693743768596</v>
+        <v>219.74979288582023</v>
       </c>
       <c r="G35" s="2">
         <f>F35/D35</f>
-        <v>1.0511819658212811</v>
+        <v>1.3080344814632157</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D36" s="1">
-        <v>168</v>
+        <v>108</v>
       </c>
       <c r="E36" s="9">
-        <v>2.93</v>
+        <v>2.66</v>
       </c>
       <c r="F36" s="7">
         <f>1000/E36/1.757</f>
-        <v>194.24981691954756</v>
+        <v>213.96690359935124</v>
       </c>
       <c r="G36" s="2">
         <f>F36/D36</f>
-        <v>1.1562489102354021</v>
+        <v>1.9811750333273264</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="D37" s="1">
-        <v>240</v>
+        <v>144</v>
       </c>
       <c r="E37" s="9">
-        <v>3.08</v>
+        <v>2.69</v>
       </c>
       <c r="F37" s="7">
         <f>1000/E37/1.757</f>
-        <v>184.78959856307608</v>
+        <v>211.58065560381945</v>
       </c>
       <c r="G37" s="2">
         <f>F37/D37</f>
-        <v>0.76995666067948365</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1.4693101083598572</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>74</v>
       </c>
       <c r="D38" s="1">
-        <v>144</v>
+        <v>288</v>
       </c>
       <c r="E38" s="9">
-        <v>3.74</v>
-      </c>
-      <c r="F38" s="6">
-        <v>152</v>
+        <v>2.79</v>
+      </c>
+      <c r="F38" s="7">
+        <f>1000/E38/1.757</f>
+        <v>203.99711956067179</v>
       </c>
       <c r="G38" s="2">
         <f>F38/D38</f>
-        <v>1.0555555555555556</v>
+        <v>0.7083233318078882</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D39" s="1">
-        <v>120</v>
+        <v>192</v>
       </c>
       <c r="E39" s="9">
-        <v>3.77</v>
+        <v>2.82</v>
       </c>
       <c r="F39" s="7">
         <f>1000/E39/1.757</f>
-        <v>150.96869060325579</v>
+        <v>201.82693743768596</v>
       </c>
       <c r="G39" s="2">
         <f>F39/D39</f>
-        <v>1.2580724216937982</v>
+        <v>1.0511819658212811</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D40" s="1">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="E40" s="9">
-        <v>3.827</v>
+        <v>2.93</v>
       </c>
       <c r="F40" s="7">
         <f>1000/E40/1.757</f>
-        <v>148.72013681062825</v>
+        <v>194.24981691954756</v>
       </c>
       <c r="G40" s="2">
         <f>F40/D40</f>
-        <v>0.826222982281268</v>
+        <v>1.1562489102354021</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D41" s="1">
-        <v>176</v>
+        <v>240</v>
       </c>
       <c r="E41" s="9">
-        <v>4.1900000000000004</v>
+        <v>3.08</v>
       </c>
       <c r="F41" s="7">
         <f>1000/E41/1.757</f>
-        <v>135.83579082918243</v>
+        <v>184.78959856307608</v>
       </c>
       <c r="G41" s="2">
         <f>F41/D41</f>
-        <v>0.7717942660749002</v>
+        <v>0.76995666067948365</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="D42" s="1">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E42" s="9">
-        <v>4.4000000000000004</v>
+        <v>3.74</v>
       </c>
       <c r="F42" s="6">
-        <f>1000/E42/1.757</f>
-        <v>129.35271899415326</v>
+        <v>152</v>
       </c>
       <c r="G42" s="2">
         <f>F42/D42</f>
-        <v>0.95112293378053869</v>
+        <v>1.0555555555555556</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D43" s="1">
-        <v>192</v>
+        <v>120</v>
       </c>
       <c r="E43" s="9">
-        <v>4.43</v>
+        <v>3.77</v>
       </c>
       <c r="F43" s="7">
         <f>1000/E43/1.757</f>
-        <v>128.4767412131545</v>
+        <v>150.96869060325579</v>
       </c>
       <c r="G43" s="2">
         <f>F43/D43</f>
-        <v>0.66914969381851297</v>
+        <v>1.2580724216937982</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D44" s="1">
-        <v>108</v>
+        <v>180</v>
       </c>
       <c r="E44" s="9">
-        <v>4.57</v>
+        <v>3.827</v>
       </c>
       <c r="F44" s="7">
         <f>1000/E44/1.757</f>
-        <v>124.54091106658082</v>
+        <v>148.72013681062825</v>
       </c>
       <c r="G44" s="2">
         <f>F44/D44</f>
-        <v>1.1531565839498223</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.826222982281268</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D45" s="1">
-        <v>128</v>
+        <v>176</v>
       </c>
       <c r="E45" s="9">
-        <v>4.71</v>
-      </c>
-      <c r="F45" s="6">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="F45" s="7">
         <f>1000/E45/1.757</f>
-        <v>120.83905808371006</v>
+        <v>135.83579082918243</v>
       </c>
       <c r="G45" s="2">
         <f>F45/D45</f>
-        <v>0.94405514127898482</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+        <v>0.7717942660749002</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D46" s="1">
-        <v>168</v>
+        <v>136</v>
       </c>
       <c r="E46" s="9">
-        <v>4.84</v>
-      </c>
-      <c r="F46" s="7">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="F46" s="6">
         <f>1000/E46/1.757</f>
-        <v>117.5933809037757</v>
+        <v>129.35271899415326</v>
       </c>
       <c r="G46" s="2">
         <f>F46/D46</f>
-        <v>0.69996060061771248</v>
+        <v>0.95112293378053869</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>82</v>
+        <v>37</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="D47" s="1">
         <v>192</v>
       </c>
       <c r="E47" s="9">
-        <v>5.0199999999999996</v>
+        <v>4.43</v>
       </c>
       <c r="F47" s="7">
         <f>1000/E47/1.757</f>
-        <v>113.37688517415825</v>
+        <v>128.4767412131545</v>
       </c>
       <c r="G47" s="2">
         <f>F47/D47</f>
-        <v>0.59050461028207424</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.66914969381851297</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
-        <v>69</v>
+        <v>19</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>67</v>
+        <v>7</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="D48" s="1">
-        <v>144</v>
+        <v>108</v>
       </c>
       <c r="E48" s="9">
-        <v>5.05</v>
-      </c>
-      <c r="F48" s="6">
+        <v>4.57</v>
+      </c>
+      <c r="F48" s="7">
         <f>1000/E48/1.757</f>
-        <v>112.70335912361868</v>
+        <v>124.54091106658082</v>
       </c>
       <c r="G48" s="2">
         <f>F48/D48</f>
-        <v>0.78266221613624087</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1.1531565839498223</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D49" s="1">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="E49" s="9">
-        <v>5.21</v>
-      </c>
-      <c r="F49" s="7">
+        <v>4.71</v>
+      </c>
+      <c r="F49" s="6">
         <f>1000/E49/1.757</f>
-        <v>109.24221949602196</v>
+        <v>120.83905808371006</v>
       </c>
       <c r="G49" s="2">
         <f>F49/D49</f>
-        <v>1.3005026130478805</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.94405514127898482</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D50" s="1">
-        <v>80</v>
+        <v>168</v>
       </c>
       <c r="E50" s="9">
-        <v>5.32</v>
-      </c>
-      <c r="F50" s="6">
+        <v>4.84</v>
+      </c>
+      <c r="F50" s="7">
         <f>1000/E50/1.757</f>
-        <v>106.98345179967562</v>
+        <v>117.5933809037757</v>
       </c>
       <c r="G50" s="2">
         <f>F50/D50</f>
-        <v>1.3372931474959453</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.69996060061771248</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>37</v>
+        <v>82</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="D51" s="1">
-        <v>136</v>
+        <v>192</v>
       </c>
       <c r="E51" s="9">
-        <v>5.57</v>
-      </c>
-      <c r="F51" s="6">
+        <v>5.0199999999999996</v>
+      </c>
+      <c r="F51" s="7">
         <f>1000/E51/1.757</f>
-        <v>102.18168107258067</v>
+        <v>113.37688517415825</v>
       </c>
       <c r="G51" s="2">
         <f>F51/D51</f>
-        <v>0.75133589023956382</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+        <v>0.59050461028207424</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="D52" s="1">
-        <v>108</v>
+        <v>144</v>
       </c>
       <c r="E52" s="9">
-        <v>6</v>
-      </c>
-      <c r="F52" s="7">
+        <v>5.05</v>
+      </c>
+      <c r="F52" s="6">
         <f>1000/E52/1.757</f>
-        <v>94.858660595712394</v>
+        <v>112.70335912361868</v>
       </c>
       <c r="G52" s="2">
         <f>F52/D52</f>
-        <v>0.87832093144178147</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.78266221613624087</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D53" s="1">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E53" s="9">
-        <v>6.38</v>
-      </c>
-      <c r="F53" s="6">
+        <v>5.21</v>
+      </c>
+      <c r="F53" s="7">
         <f>1000/E53/1.757</f>
-        <v>89.208771720105702</v>
+        <v>109.24221949602196</v>
       </c>
       <c r="G53" s="2">
         <f>F53/D53</f>
-        <v>1.1151096465013213</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1.3005026130478805</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>82</v>
+        <v>34</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="D54" s="1">
-        <v>144</v>
+        <v>80</v>
       </c>
       <c r="E54" s="9">
-        <v>6.69</v>
-      </c>
-      <c r="F54" s="7">
+        <v>5.32</v>
+      </c>
+      <c r="F54" s="6">
         <f>1000/E54/1.757</f>
-        <v>85.075031924405735</v>
+        <v>106.98345179967562</v>
       </c>
       <c r="G54" s="2">
         <f>F54/D54</f>
-        <v>0.5907988328083732</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1.3372931474959453</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D55" s="1">
-        <v>72</v>
+        <v>136</v>
       </c>
       <c r="E55" s="9">
-        <v>7.54</v>
-      </c>
-      <c r="F55" s="7">
+        <v>5.57</v>
+      </c>
+      <c r="F55" s="6">
         <f>1000/E55/1.757</f>
-        <v>75.484345301627897</v>
+        <v>102.18168107258067</v>
       </c>
       <c r="G55" s="2">
         <f>F55/D55</f>
-        <v>1.0483936847448319</v>
+        <v>0.75133589023956382</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D56" s="1">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="E56" s="9">
-        <v>8.11</v>
+        <v>6</v>
       </c>
       <c r="F56" s="7">
         <f>1000/E56/1.757</f>
-        <v>70.179033732956157</v>
+        <v>94.858660595712394</v>
       </c>
       <c r="G56" s="2">
         <f>F56/D56</f>
-        <v>0.58482528110796794</v>
+        <v>0.87832093144178147</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D57" s="1">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E57" s="9">
-        <v>8.49</v>
+        <v>6.38</v>
       </c>
       <c r="F57" s="6">
         <f>1000/E57/1.757</f>
-        <v>67.037922682482261</v>
+        <v>89.208771720105702</v>
       </c>
       <c r="G57" s="2">
         <f>F57/D57</f>
-        <v>0.93108225947892032</v>
+        <v>1.1151096465013213</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>7</v>
+        <v>82</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="D58" s="1">
-        <v>72</v>
+        <v>144</v>
       </c>
       <c r="E58" s="9">
-        <v>8.7100000000000009</v>
+        <v>6.69</v>
       </c>
       <c r="F58" s="7">
         <f>1000/E58/1.757</f>
-        <v>65.344657126782351</v>
+        <v>85.075031924405735</v>
       </c>
       <c r="G58" s="2">
         <f>F58/D58</f>
-        <v>0.90756468231642151</v>
+        <v>0.5907988328083732</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D59" s="1">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="E59" s="9">
-        <v>9.19</v>
+        <v>7.54</v>
       </c>
       <c r="F59" s="7">
         <f>1000/E59/1.757</f>
-        <v>61.931660889474905</v>
+        <v>75.484345301627897</v>
       </c>
       <c r="G59" s="2">
         <f>F59/D59</f>
-        <v>0.73728167725565363</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1.0483936847448319</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D60" s="1">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="E60" s="9">
-        <v>9.2799999999999994</v>
-      </c>
-      <c r="F60" s="6">
+        <v>8.11</v>
+      </c>
+      <c r="F60" s="7">
         <f>1000/E60/1.757</f>
-        <v>61.331030557572667</v>
+        <v>70.179033732956157</v>
       </c>
       <c r="G60" s="2">
         <f>F60/D60</f>
-        <v>0.76663788196965832</v>
+        <v>0.58482528110796794</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="D61" s="1">
-        <v>144</v>
+        <v>72</v>
       </c>
       <c r="E61" s="9">
-        <v>9.41</v>
-      </c>
-      <c r="F61" s="8">
+        <v>8.49</v>
+      </c>
+      <c r="F61" s="6">
         <f>1000/E61/1.757</f>
-        <v>60.483736830422359</v>
+        <v>67.037922682482261</v>
       </c>
       <c r="G61" s="2">
         <f>F61/D61</f>
-        <v>0.42002595021126637</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.93108225947892032</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
-        <v>78</v>
+        <v>22</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D62" s="1">
-        <v>128</v>
+        <v>72</v>
       </c>
       <c r="E62" s="9">
-        <v>9.49</v>
-      </c>
-      <c r="F62" s="6">
+        <v>8.7100000000000009</v>
+      </c>
+      <c r="F62" s="7">
         <f>1000/E62/1.757</f>
-        <v>59.973863390334493</v>
+        <v>65.344657126782351</v>
       </c>
       <c r="G62" s="2">
         <f>F62/D62</f>
-        <v>0.46854580773698823</v>
+        <v>0.90756468231642151</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D63" s="1">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="E63" s="9">
-        <v>10.44</v>
+        <v>9.19</v>
       </c>
       <c r="F63" s="7">
         <f>1000/E63/1.757</f>
-        <v>54.516471606731265</v>
+        <v>61.931660889474905</v>
       </c>
       <c r="G63" s="2">
         <f>F63/D63</f>
-        <v>0.75717321676015648</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+        <v>0.73728167725565363</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D64" s="1">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E64" s="9">
-        <v>11.83</v>
-      </c>
-      <c r="F64" s="7">
+        <v>9.2799999999999994</v>
+      </c>
+      <c r="F64" s="6">
         <f>1000/E64/1.757</f>
-        <v>48.110901401037566</v>
+        <v>61.331030557572667</v>
       </c>
       <c r="G64" s="2">
         <f>F64/D64</f>
-        <v>0.66820696390329948</v>
+        <v>0.76663788196965832</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="D65" s="1">
-        <v>80</v>
+        <v>144</v>
       </c>
       <c r="E65" s="9">
-        <v>12.2</v>
-      </c>
-      <c r="F65" s="6">
+        <v>9.41</v>
+      </c>
+      <c r="F65" s="8">
         <f>1000/E65/1.757</f>
-        <v>46.651800292973313</v>
+        <v>60.483736830422359</v>
       </c>
       <c r="G65" s="2">
         <f>F65/D65</f>
-        <v>0.58314750366216639</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+        <v>0.42002595021126637</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D66" s="1">
-        <v>48</v>
+        <v>128</v>
       </c>
       <c r="E66" s="9">
-        <v>14.9</v>
-      </c>
-      <c r="F66" s="7">
+        <v>9.49</v>
+      </c>
+      <c r="F66" s="6">
         <f>1000/E66/1.757</f>
-        <v>38.198118360689556</v>
+        <v>59.973863390334493</v>
       </c>
       <c r="G66" s="2">
         <f>F66/D66</f>
-        <v>0.7957941325143657</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.46854580773698823</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D67" s="1">
         <v>72</v>
       </c>
       <c r="E67" s="9">
-        <v>16.8</v>
-      </c>
-      <c r="F67" s="6">
+        <v>10.44</v>
+      </c>
+      <c r="F67" s="7">
         <f>1000/E67/1.757</f>
-        <v>33.878093069897282</v>
+        <v>54.516471606731265</v>
       </c>
       <c r="G67" s="2">
         <f>F67/D67</f>
-        <v>0.47052907041524006</v>
+        <v>0.75717321676015648</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>52</v>
@@ -2422,45 +2446,45 @@
         <v>72</v>
       </c>
       <c r="E68" s="9">
-        <v>18.329999999999998</v>
+        <v>11.83</v>
       </c>
       <c r="F68" s="7">
         <f>1000/E68/1.757</f>
-        <v>31.050298067336303</v>
+        <v>48.110901401037566</v>
       </c>
       <c r="G68" s="2">
         <f>F68/D68</f>
-        <v>0.43125413982411531</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
+        <v>0.66820696390329948</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D69" s="1">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E69" s="9">
-        <v>19.02</v>
-      </c>
-      <c r="F69" s="7">
+        <v>12.2</v>
+      </c>
+      <c r="F69" s="6">
         <f>1000/E69/1.757</f>
-        <v>29.923867695808326</v>
+        <v>46.651800292973313</v>
       </c>
       <c r="G69" s="2">
         <f>F69/D69</f>
-        <v>0.4156092735528934</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.58314750366216639</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>7</v>
@@ -2469,271 +2493,273 @@
         <v>55</v>
       </c>
       <c r="D70" s="1">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="E70" s="9">
-        <v>25.3</v>
-      </c>
-      <c r="F70" s="6">
+        <v>14.9</v>
+      </c>
+      <c r="F70" s="7">
         <f>1000/E70/1.757</f>
-        <v>22.496125042461436</v>
+        <v>38.198118360689556</v>
       </c>
       <c r="G70" s="2">
         <f>F70/D70</f>
-        <v>0.70300390757691988</v>
+        <v>0.7957941325143657</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D71" s="1">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="E71" s="9">
-        <v>27.52</v>
+        <v>16.8</v>
       </c>
       <c r="F71" s="6">
         <f>1000/E71/1.757</f>
-        <v>20.681394025227995</v>
+        <v>33.878093069897282</v>
       </c>
       <c r="G71" s="2">
         <f>F71/D71</f>
-        <v>0.43086237552558321</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.47052907041524006</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="D72" s="1">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="E72" s="9">
-        <v>33</v>
-      </c>
-      <c r="F72" s="6">
+        <v>18.329999999999998</v>
+      </c>
+      <c r="F72" s="7">
         <f>1000/E72/1.757</f>
-        <v>17.247029199220435</v>
+        <v>31.050298067336303</v>
       </c>
       <c r="G72" s="2">
         <f>F72/D72</f>
-        <v>0.7186262166341848</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.43125413982411531</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D73" s="1">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="E73" s="9">
-        <v>42.9</v>
-      </c>
-      <c r="F73" s="6">
+        <v>19.02</v>
+      </c>
+      <c r="F73" s="7">
         <f>1000/E73/1.757</f>
-        <v>13.266945537861874</v>
+        <v>29.923867695808326</v>
       </c>
       <c r="G73" s="2">
         <f>F73/D73</f>
-        <v>0.41459204805818356</v>
+        <v>0.4156092735528934</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="D74" s="1">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E74" s="9">
-        <v>53.4</v>
+        <v>25.3</v>
       </c>
       <c r="F74" s="6">
         <f>1000/E74/1.757</f>
-        <v>10.65827647142836</v>
+        <v>22.496125042461436</v>
       </c>
       <c r="G74" s="2">
         <f>F74/D74</f>
-        <v>0.44409485297618168</v>
+        <v>0.70300390757691988</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D75" s="1">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="E75" s="9">
-        <v>67</v>
-      </c>
-      <c r="F75" s="4">
+        <v>27.52</v>
+      </c>
+      <c r="F75" s="6">
         <f>1000/E75/1.757</f>
-        <v>8.4948054264817063</v>
+        <v>20.681394025227995</v>
       </c>
       <c r="G75" s="2">
         <f>F75/D75</f>
-        <v>0.53092533915510665</v>
+        <v>0.43086237552558321</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D76" s="1">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E76" s="9">
-        <v>71.900000000000006</v>
-      </c>
-      <c r="F76" s="4">
+        <v>33</v>
+      </c>
+      <c r="F76" s="6">
         <f>1000/E76/1.757</f>
-        <v>7.9158826644544416</v>
+        <v>17.247029199220435</v>
       </c>
       <c r="G76" s="2">
         <f>F76/D76</f>
-        <v>0.4947426665284026</v>
+        <v>0.7186262166341848</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D77" s="1">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="E77" s="9">
-        <v>73.599999999999994</v>
-      </c>
-      <c r="F77" s="4">
+        <v>42.9</v>
+      </c>
+      <c r="F77" s="6">
         <f>1000/E77/1.757</f>
-        <v>7.7330429833461194</v>
+        <v>13.266945537861874</v>
       </c>
       <c r="G77" s="2">
         <f>F77/D77</f>
-        <v>0.12888404972243533</v>
+        <v>0.41459204805818356</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D78" s="6">
-        <v>16</v>
+        <v>62</v>
+      </c>
+      <c r="D78" s="1">
+        <v>24</v>
       </c>
       <c r="E78" s="9">
-        <v>74</v>
-      </c>
-      <c r="F78" s="4">
+        <v>53.4</v>
+      </c>
+      <c r="F78" s="6">
         <f>1000/E78/1.757</f>
-        <v>7.691242751003708</v>
+        <v>10.65827647142836</v>
       </c>
       <c r="G78" s="2">
         <f>F78/D78</f>
-        <v>0.48070267193773175</v>
+        <v>0.44409485297618168</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D79" s="6">
-        <v>20</v>
+        <v>56</v>
+      </c>
+      <c r="D79" s="1">
+        <v>16</v>
       </c>
       <c r="E79" s="9">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="F79" s="4">
         <f>1000/E79/1.757</f>
-        <v>7.2968200458240311</v>
+        <v>8.4948054264817063</v>
       </c>
       <c r="G79" s="2">
         <f>F79/D79</f>
-        <v>0.36484100229120153</v>
+        <v>0.53092533915510665</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>71</v>
+        <v>26</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D80" s="6">
-        <v>60</v>
+        <v>56</v>
+      </c>
+      <c r="D80" s="1">
+        <v>16</v>
       </c>
       <c r="E80" s="9">
-        <v>79.099999999999994</v>
+        <v>71.900000000000006</v>
       </c>
       <c r="F80" s="4">
-        <v>7.2</v>
-      </c>
-      <c r="G80" s="1">
-        <v>0.12</v>
+        <f>1000/E80/1.757</f>
+        <v>7.9158826644544416</v>
+      </c>
+      <c r="G80" s="2">
+        <f>F80/D80</f>
+        <v>0.4947426665284026</v>
       </c>
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>7</v>
@@ -2741,244 +2767,246 @@
       <c r="C81" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D81" s="6">
-        <v>20</v>
+      <c r="D81" s="1">
+        <v>60</v>
       </c>
       <c r="E81" s="9">
-        <v>82.4</v>
+        <v>73.599999999999994</v>
       </c>
       <c r="F81" s="4">
-        <v>6.9</v>
-      </c>
-      <c r="G81" s="1">
-        <v>0.35</v>
+        <f>1000/E81/1.757</f>
+        <v>7.7330429833461194</v>
+      </c>
+      <c r="G81" s="2">
+        <f>F81/D81</f>
+        <v>0.12888404972243533</v>
       </c>
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D82" s="6">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="E82" s="9">
-        <v>85.5</v>
+        <v>74</v>
       </c>
       <c r="F82" s="4">
         <f>1000/E82/1.757</f>
-        <v>6.6567481119798169</v>
+        <v>7.691242751003708</v>
       </c>
       <c r="G82" s="2">
         <f>F82/D82</f>
-        <v>0.11094580186633028</v>
+        <v>0.48070267193773175</v>
       </c>
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D83" s="6">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E83" s="9">
-        <v>93.5</v>
+        <v>78</v>
       </c>
       <c r="F83" s="4">
         <f>1000/E83/1.757</f>
-        <v>6.0871867761954475</v>
+        <v>7.2968200458240311</v>
       </c>
       <c r="G83" s="2">
         <f>F83/D83</f>
-        <v>0.38044917351221547</v>
-      </c>
-    </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.35">
+        <v>0.36484100229120153</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D84" s="6">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="E84" s="9">
-        <v>107.1</v>
-      </c>
-      <c r="F84" s="3">
-        <f>1000/E84/1.757</f>
-        <v>5.314210677630947</v>
-      </c>
-      <c r="G84" s="2">
-        <f>F84/D84</f>
-        <v>0.33213816735193419</v>
-      </c>
-    </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.35">
+        <v>79.099999999999994</v>
+      </c>
+      <c r="F84" s="4">
+        <v>7.2</v>
+      </c>
+      <c r="G84" s="1">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D85" s="6">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E85" s="9">
-        <v>107.2</v>
-      </c>
-      <c r="F85" s="3">
-        <f>1000/E85/1.757</f>
-        <v>5.3092533915510671</v>
-      </c>
-      <c r="G85" s="2">
-        <f>F85/D85</f>
-        <v>0.3318283369719417</v>
-      </c>
-    </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.35">
+        <v>82.4</v>
+      </c>
+      <c r="F85" s="4">
+        <v>6.9</v>
+      </c>
+      <c r="G85" s="1">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D86" s="6">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="E86" s="9">
-        <v>108.1</v>
-      </c>
-      <c r="F86" s="3">
+        <v>85.5</v>
+      </c>
+      <c r="F86" s="4">
         <f>1000/E86/1.757</f>
-        <v>5.265050541852677</v>
+        <v>6.6567481119798169</v>
       </c>
       <c r="G86" s="2">
         <f>F86/D86</f>
-        <v>0.32906565886579231</v>
-      </c>
-    </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.35">
+        <v>0.11094580186633028</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D87" s="6">
         <v>16</v>
       </c>
       <c r="E87" s="9">
-        <v>121</v>
-      </c>
-      <c r="F87" s="3">
+        <v>93.5</v>
+      </c>
+      <c r="F87" s="4">
         <f>1000/E87/1.757</f>
-        <v>4.7037352361510276</v>
+        <v>6.0871867761954475</v>
       </c>
       <c r="G87" s="2">
         <f>F87/D87</f>
-        <v>0.29398345225943923</v>
-      </c>
-    </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.38044917351221547</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D88" s="6">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E88" s="9">
-        <v>124.8</v>
-      </c>
-      <c r="F88" s="4">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="G88" s="1">
-        <v>0.23</v>
+        <v>107.1</v>
+      </c>
+      <c r="F88" s="3">
+        <f>1000/E88/1.757</f>
+        <v>5.314210677630947</v>
+      </c>
+      <c r="G88" s="2">
+        <f>F88/D88</f>
+        <v>0.33213816735193419</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
       <c r="P88" s="2"/>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
-        <v>71</v>
+        <v>29</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D89" s="6">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="E89" s="9">
-        <v>124.6</v>
-      </c>
-      <c r="F89" s="4">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="G89" s="1">
-        <v>0.08</v>
+        <v>107.2</v>
+      </c>
+      <c r="F89" s="3">
+        <f>1000/E89/1.757</f>
+        <v>5.3092533915510671</v>
+      </c>
+      <c r="G89" s="2">
+        <f>F89/D89</f>
+        <v>0.3318283369719417</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" s="2"/>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C90" s="5">
-        <v>8051</v>
+        <v>30</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>57</v>
       </c>
       <c r="D90" s="6">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E90" s="9">
-        <v>254</v>
-      </c>
-      <c r="F90" s="4">
+        <v>108.1</v>
+      </c>
+      <c r="F90" s="3">
         <f>1000/E90/1.757</f>
-        <v>2.2407557621034426</v>
+        <v>5.265050541852677</v>
       </c>
       <c r="G90" s="2">
         <f>F90/D90</f>
-        <v>9.3364823420976781E-2</v>
+        <v>0.32906565886579231</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -2986,63 +3014,159 @@
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C91" s="5">
-        <v>8051</v>
-      </c>
-      <c r="D91" s="1">
+        <v>30</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D91" s="6">
         <v>16</v>
       </c>
       <c r="E91" s="9">
-        <v>883</v>
+        <v>121</v>
       </c>
       <c r="F91" s="3">
         <f>1000/E91/1.757</f>
-        <v>0.64456621016339111</v>
+        <v>4.7037352361510276</v>
       </c>
       <c r="G91" s="2">
         <f>F91/D91</f>
-        <v>4.0285388135211944E-2</v>
+        <v>0.29398345225943923</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
       <c r="P91" s="2"/>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>32</v>
+        <v>71</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C92" s="5">
-        <v>8051</v>
-      </c>
-      <c r="D92" s="1">
-        <v>16</v>
+        <v>8</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D92" s="6">
+        <v>20</v>
       </c>
       <c r="E92" s="9">
-        <v>884</v>
-      </c>
-      <c r="F92" s="3">
-        <f>1000/E92/1.757</f>
-        <v>0.64383706286682618</v>
-      </c>
-      <c r="G92" s="2">
-        <f>F92/D92</f>
-        <v>4.0239816429176636E-2</v>
+        <v>124.8</v>
+      </c>
+      <c r="F92" s="4">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G92" s="1">
+        <v>0.23</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
       <c r="P92" s="2"/>
     </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D93" s="6">
+        <v>60</v>
+      </c>
+      <c r="E93" s="9">
+        <v>124.6</v>
+      </c>
+      <c r="F93" s="4">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G93" s="1">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C94" s="5">
+        <v>8051</v>
+      </c>
+      <c r="D94" s="6">
+        <v>24</v>
+      </c>
+      <c r="E94" s="9">
+        <v>254</v>
+      </c>
+      <c r="F94" s="4">
+        <f>1000/E94/1.757</f>
+        <v>2.2407557621034426</v>
+      </c>
+      <c r="G94" s="2">
+        <f>F94/D94</f>
+        <v>9.3364823420976781E-2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A95" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C95" s="5">
+        <v>8051</v>
+      </c>
+      <c r="D95" s="1">
+        <v>16</v>
+      </c>
+      <c r="E95" s="9">
+        <v>883</v>
+      </c>
+      <c r="F95" s="3">
+        <f>1000/E95/1.757</f>
+        <v>0.64456621016339111</v>
+      </c>
+      <c r="G95" s="2">
+        <f>F95/D95</f>
+        <v>4.0285388135211944E-2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A96" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C96" s="5">
+        <v>8051</v>
+      </c>
+      <c r="D96" s="1">
+        <v>16</v>
+      </c>
+      <c r="E96" s="9">
+        <v>884</v>
+      </c>
+      <c r="F96" s="3">
+        <f>1000/E96/1.757</f>
+        <v>0.64383706286682618</v>
+      </c>
+      <c r="G96" s="2">
+        <f>F96/D96</f>
+        <v>4.0239816429176636E-2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H42" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H92">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H96">
       <sortCondition descending="1" ref="F1:F42"/>
     </sortState>
   </autoFilter>

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\__my_github\dhrystone_score\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BBE6C7F-579F-4AC6-9892-A5F54641EAAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A23F03E2-D764-4A3E-B2D5-18EBACB567C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="840" yWindow="-108" windowWidth="29988" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -800,11 +800,11 @@
         <v>2.3400000000000001E-2</v>
       </c>
       <c r="F2" s="7">
-        <f>1000/E2/1.757</f>
+        <f t="shared" ref="F2:F41" si="0">1000/E2/1.757</f>
         <v>24322.733486080102</v>
       </c>
       <c r="G2" s="2">
-        <f>F2/D2</f>
+        <f t="shared" ref="G2:G33" si="1">F2/D2</f>
         <v>5.5914329853057705</v>
       </c>
     </row>
@@ -825,11 +825,11 @@
         <v>0.05</v>
       </c>
       <c r="F3" s="7">
-        <f>1000/E3/1.757</f>
+        <f t="shared" si="0"/>
         <v>11383.039271485488</v>
       </c>
       <c r="G3" s="2">
-        <f>F3/D3</f>
+        <f t="shared" si="1"/>
         <v>2.6167906371231004</v>
       </c>
     </row>
@@ -850,11 +850,11 @@
         <v>0.249</v>
       </c>
       <c r="F4" s="7">
-        <f>1000/E4/1.757</f>
+        <f t="shared" si="0"/>
         <v>2285.7508577280096</v>
       </c>
       <c r="G4" s="2">
-        <f>F4/D4</f>
+        <f t="shared" si="1"/>
         <v>2.2857508577280097</v>
       </c>
     </row>
@@ -875,11 +875,11 @@
         <v>0.32900000000000001</v>
       </c>
       <c r="F5" s="6">
-        <f>1000/E5/1.757</f>
+        <f t="shared" si="0"/>
         <v>1729.9451780373081</v>
       </c>
       <c r="G5" s="2">
-        <f>F5/D5</f>
+        <f t="shared" si="1"/>
         <v>2.1624314725466349</v>
       </c>
     </row>
@@ -900,11 +900,11 @@
         <v>0.40300000000000002</v>
       </c>
       <c r="F6" s="6">
-        <f>1000/E6/1.757</f>
+        <f t="shared" si="0"/>
         <v>1412.2877508046511</v>
       </c>
       <c r="G6" s="2">
-        <f>F6/D6</f>
+        <f t="shared" si="1"/>
         <v>2.9422661475096898</v>
       </c>
     </row>
@@ -925,11 +925,11 @@
         <v>0.41499999999999998</v>
       </c>
       <c r="F7" s="7">
-        <f>1000/E7/1.757</f>
+        <f t="shared" si="0"/>
         <v>1371.4505146368058</v>
       </c>
       <c r="G7" s="2">
-        <f>F7/D7</f>
+        <f t="shared" si="1"/>
         <v>2.2857508577280097</v>
       </c>
     </row>
@@ -950,11 +950,11 @@
         <v>0.42</v>
       </c>
       <c r="F8" s="7">
-        <f>1000/E8/1.757</f>
+        <f t="shared" si="0"/>
         <v>1355.1237227958916</v>
       </c>
       <c r="G8" s="2">
-        <f>F8/D8</f>
+        <f t="shared" si="1"/>
         <v>1.3551237227958917</v>
       </c>
     </row>
@@ -975,11 +975,11 @@
         <v>0.61</v>
       </c>
       <c r="F9" s="6">
-        <f>1000/E9/1.757</f>
+        <f t="shared" si="0"/>
         <v>933.03600585946617</v>
       </c>
       <c r="G9" s="2">
-        <f>F9/D9</f>
+        <f t="shared" si="1"/>
         <v>1.9438250122072211</v>
       </c>
     </row>
@@ -1000,11 +1000,11 @@
         <v>0.68300000000000005</v>
       </c>
       <c r="F10" s="6">
-        <f>1000/E10/1.757</f>
+        <f t="shared" si="0"/>
         <v>833.31180611167554</v>
       </c>
       <c r="G10" s="2">
-        <f>F10/D10</f>
+        <f t="shared" si="1"/>
         <v>1.0416397576395944</v>
       </c>
     </row>
@@ -1025,11 +1025,11 @@
         <v>0.70099999999999996</v>
       </c>
       <c r="F11" s="7">
-        <f>1000/E11/1.757</f>
+        <f t="shared" si="0"/>
         <v>811.91435602606896</v>
       </c>
       <c r="G11" s="2">
-        <f>F11/D11</f>
+        <f t="shared" si="1"/>
         <v>1.3531905933767816</v>
       </c>
     </row>
@@ -1044,18 +1044,18 @@
         <v>96</v>
       </c>
       <c r="D12" s="1">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="E12" s="9">
         <v>0.83199999999999996</v>
       </c>
       <c r="F12" s="7">
-        <f>1000/E12/1.757</f>
+        <f t="shared" si="0"/>
         <v>684.07687929600286</v>
       </c>
       <c r="G12" s="2">
-        <f>F12/D12</f>
-        <v>1.5201708428800063</v>
+        <f t="shared" si="1"/>
+        <v>1.5547201802181883</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1075,11 +1075,11 @@
         <v>1.08</v>
       </c>
       <c r="F13" s="6">
-        <f>1000/E13/1.757</f>
+        <f t="shared" si="0"/>
         <v>526.99255886506887</v>
       </c>
       <c r="G13" s="2">
-        <f>F13/D13</f>
+        <f t="shared" si="1"/>
         <v>1.3174813971626722</v>
       </c>
     </row>
@@ -1100,11 +1100,11 @@
         <v>1.1499999999999999</v>
       </c>
       <c r="F14" s="7">
-        <f>1000/E14/1.757</f>
+        <f t="shared" si="0"/>
         <v>494.91475093415164</v>
       </c>
       <c r="G14" s="2">
-        <f>F14/D14</f>
+        <f t="shared" si="1"/>
         <v>1.3448770405819339</v>
       </c>
     </row>
@@ -1125,11 +1125,11 @@
         <v>1.21</v>
       </c>
       <c r="F15" s="7">
-        <f>1000/E15/1.757</f>
+        <f t="shared" si="0"/>
         <v>470.37352361510278</v>
       </c>
       <c r="G15" s="2">
-        <f>F15/D15</f>
+        <f t="shared" si="1"/>
         <v>1.3065931211530633</v>
       </c>
     </row>
@@ -1150,11 +1150,11 @@
         <v>1.232</v>
       </c>
       <c r="F16" s="7">
-        <f>1000/E16/1.757</f>
+        <f t="shared" si="0"/>
         <v>461.97399640769027</v>
       </c>
       <c r="G16" s="2">
-        <f>F16/D16</f>
+        <f t="shared" si="1"/>
         <v>1.4436687387740321</v>
       </c>
     </row>
@@ -1175,11 +1175,11 @@
         <v>1.4</v>
       </c>
       <c r="F17" s="7">
-        <f>1000/E17/1.757</f>
+        <f t="shared" si="0"/>
         <v>406.53711683876742</v>
       </c>
       <c r="G17" s="2">
-        <f>F17/D17</f>
+        <f t="shared" si="1"/>
         <v>1.4946217530837038</v>
       </c>
     </row>
@@ -1200,11 +1200,11 @@
         <v>1.464</v>
       </c>
       <c r="F18" s="7">
-        <f>1000/E18/1.757</f>
+        <f t="shared" si="0"/>
         <v>388.76500244144421</v>
       </c>
       <c r="G18" s="2">
-        <f>F18/D18</f>
+        <f t="shared" si="1"/>
         <v>1.5550600097657767</v>
       </c>
     </row>
@@ -1219,18 +1219,18 @@
         <v>96</v>
       </c>
       <c r="D19" s="1">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="E19" s="9">
         <v>1.4690000000000001</v>
       </c>
       <c r="F19" s="7">
-        <f>1000/E19/1.757</f>
+        <f t="shared" si="0"/>
         <v>387.44177234463876</v>
       </c>
       <c r="G19" s="2">
-        <f>F19/D19</f>
-        <v>0.86098171632141951</v>
+        <f t="shared" si="1"/>
+        <v>0.88054948260145172</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
@@ -1250,11 +1250,11 @@
         <v>1.49</v>
       </c>
       <c r="F20" s="7">
-        <f>1000/E20/1.757</f>
+        <f t="shared" si="0"/>
         <v>381.98118360689551</v>
       </c>
       <c r="G20" s="2">
-        <f>F20/D20</f>
+        <f t="shared" si="1"/>
         <v>1.9894853312859142</v>
       </c>
     </row>
@@ -1275,11 +1275,11 @@
         <v>1.54</v>
       </c>
       <c r="F21" s="7">
-        <f>1000/E21/1.757</f>
+        <f t="shared" si="0"/>
         <v>369.57919712615217</v>
       </c>
       <c r="G21" s="2">
-        <f>F21/D21</f>
+        <f t="shared" si="1"/>
         <v>1.2832611011324728</v>
       </c>
     </row>
@@ -1300,11 +1300,11 @@
         <v>1.59</v>
       </c>
       <c r="F22" s="7">
-        <f>1000/E22/1.757</f>
+        <f t="shared" si="0"/>
         <v>357.95720979514107</v>
       </c>
       <c r="G22" s="2">
-        <f>F22/D22</f>
+        <f t="shared" si="1"/>
         <v>1.4914883741464211</v>
       </c>
     </row>
@@ -1325,11 +1325,11 @@
         <v>1.71</v>
       </c>
       <c r="F23" s="7">
-        <f>1000/E23/1.757</f>
+        <f t="shared" si="0"/>
         <v>332.83740559899087</v>
       </c>
       <c r="G23" s="2">
-        <f>F23/D23</f>
+        <f t="shared" si="1"/>
         <v>1.1556854361076072</v>
       </c>
     </row>
@@ -1350,11 +1350,11 @@
         <v>1.76</v>
       </c>
       <c r="F24" s="7">
-        <f>1000/E24/1.757</f>
+        <f t="shared" si="0"/>
         <v>323.38179748538312</v>
       </c>
       <c r="G24" s="2">
-        <f>F24/D24</f>
+        <f t="shared" si="1"/>
         <v>1.1549349910192255</v>
       </c>
     </row>
@@ -1375,11 +1375,11 @@
         <v>1.8</v>
       </c>
       <c r="F25" s="7">
-        <f>1000/E25/1.757</f>
+        <f t="shared" si="0"/>
         <v>316.19553531904131</v>
       </c>
       <c r="G25" s="2">
-        <f>F25/D25</f>
+        <f t="shared" si="1"/>
         <v>1.1292697689965761</v>
       </c>
     </row>
@@ -1400,11 +1400,11 @@
         <v>1.8140000000000001</v>
       </c>
       <c r="F26" s="7">
-        <f>1000/E26/1.757</f>
+        <f t="shared" si="0"/>
         <v>313.7552169648701</v>
       </c>
       <c r="G26" s="2">
-        <f>F26/D26</f>
+        <f t="shared" si="1"/>
         <v>1.3073134040202921</v>
       </c>
     </row>
@@ -1425,11 +1425,11 @@
         <v>1.85</v>
       </c>
       <c r="F27" s="7">
-        <f>1000/E27/1.757</f>
+        <f t="shared" si="0"/>
         <v>307.64971004014831</v>
       </c>
       <c r="G27" s="2">
-        <f>F27/D27</f>
+        <f t="shared" si="1"/>
         <v>1.47908514442379</v>
       </c>
     </row>
@@ -1450,11 +1450,11 @@
         <v>2.06</v>
       </c>
       <c r="F28" s="7">
-        <f>1000/E28/1.757</f>
+        <f t="shared" si="0"/>
         <v>276.28736095838559</v>
       </c>
       <c r="G28" s="2">
-        <f>F28/D28</f>
+        <f t="shared" si="1"/>
         <v>1.1511973373266067</v>
       </c>
     </row>
@@ -1475,11 +1475,11 @@
         <v>2.0699999999999998</v>
       </c>
       <c r="F29" s="7">
-        <f>1000/E29/1.757</f>
+        <f t="shared" si="0"/>
         <v>274.95263940786202</v>
       </c>
       <c r="G29" s="2">
-        <f>F29/D29</f>
+        <f t="shared" si="1"/>
         <v>0.74715391143440768</v>
       </c>
     </row>
@@ -1500,11 +1500,11 @@
         <v>2.12</v>
       </c>
       <c r="F30" s="6">
-        <f>1000/E30/1.757</f>
+        <f t="shared" si="0"/>
         <v>268.46790734635579</v>
       </c>
       <c r="G30" s="2">
-        <f>F30/D30</f>
+        <f t="shared" si="1"/>
         <v>1.0487027630717023</v>
       </c>
     </row>
@@ -1525,11 +1525,11 @@
         <v>2.15</v>
       </c>
       <c r="F31" s="7">
-        <f>1000/E31/1.757</f>
+        <f t="shared" si="0"/>
         <v>264.72184352291833</v>
       </c>
       <c r="G31" s="2">
-        <f>F31/D31</f>
+        <f t="shared" si="1"/>
         <v>1.5041013836529451</v>
       </c>
     </row>
@@ -1550,11 +1550,11 @@
         <v>2.16</v>
       </c>
       <c r="F32" s="6">
-        <f>1000/E32/1.757</f>
+        <f t="shared" si="0"/>
         <v>263.49627943253444</v>
       </c>
       <c r="G32" s="2">
-        <f>F32/D32</f>
+        <f t="shared" si="1"/>
         <v>1.3174813971626722</v>
       </c>
     </row>
@@ -1575,11 +1575,11 @@
         <v>2.1880000000000002</v>
       </c>
       <c r="F33" s="7">
-        <f>1000/E33/1.757</f>
+        <f t="shared" si="0"/>
         <v>260.12429779445807</v>
       </c>
       <c r="G33" s="2">
-        <f>F33/D33</f>
+        <f t="shared" si="1"/>
         <v>1.4451349877469892</v>
       </c>
     </row>
@@ -1600,11 +1600,11 @@
         <v>2.5870000000000002</v>
       </c>
       <c r="F34" s="3">
-        <f>1000/E34/1.757</f>
+        <f t="shared" si="0"/>
         <v>220.00462449720695</v>
       </c>
       <c r="G34" s="2">
-        <f>F34/D34</f>
+        <f t="shared" ref="G34:G65" si="2">F34/D34</f>
         <v>0.88001849798882781</v>
       </c>
     </row>
@@ -1625,11 +1625,11 @@
         <v>2.59</v>
       </c>
       <c r="F35" s="7">
-        <f>1000/E35/1.757</f>
+        <f t="shared" si="0"/>
         <v>219.74979288582023</v>
       </c>
       <c r="G35" s="2">
-        <f>F35/D35</f>
+        <f t="shared" si="2"/>
         <v>1.3080344814632157</v>
       </c>
     </row>
@@ -1650,11 +1650,11 @@
         <v>2.66</v>
       </c>
       <c r="F36" s="7">
-        <f>1000/E36/1.757</f>
+        <f t="shared" si="0"/>
         <v>213.96690359935124</v>
       </c>
       <c r="G36" s="2">
-        <f>F36/D36</f>
+        <f t="shared" si="2"/>
         <v>1.9811750333273264</v>
       </c>
     </row>
@@ -1675,11 +1675,11 @@
         <v>2.69</v>
       </c>
       <c r="F37" s="7">
-        <f>1000/E37/1.757</f>
+        <f t="shared" si="0"/>
         <v>211.58065560381945</v>
       </c>
       <c r="G37" s="2">
-        <f>F37/D37</f>
+        <f t="shared" si="2"/>
         <v>1.4693101083598572</v>
       </c>
     </row>
@@ -1700,11 +1700,11 @@
         <v>2.79</v>
       </c>
       <c r="F38" s="7">
-        <f>1000/E38/1.757</f>
+        <f t="shared" si="0"/>
         <v>203.99711956067179</v>
       </c>
       <c r="G38" s="2">
-        <f>F38/D38</f>
+        <f t="shared" si="2"/>
         <v>0.7083233318078882</v>
       </c>
     </row>
@@ -1725,11 +1725,11 @@
         <v>2.82</v>
       </c>
       <c r="F39" s="7">
-        <f>1000/E39/1.757</f>
+        <f t="shared" si="0"/>
         <v>201.82693743768596</v>
       </c>
       <c r="G39" s="2">
-        <f>F39/D39</f>
+        <f t="shared" si="2"/>
         <v>1.0511819658212811</v>
       </c>
     </row>
@@ -1750,11 +1750,11 @@
         <v>2.93</v>
       </c>
       <c r="F40" s="7">
-        <f>1000/E40/1.757</f>
+        <f t="shared" si="0"/>
         <v>194.24981691954756</v>
       </c>
       <c r="G40" s="2">
-        <f>F40/D40</f>
+        <f t="shared" si="2"/>
         <v>1.1562489102354021</v>
       </c>
     </row>
@@ -1775,11 +1775,11 @@
         <v>3.08</v>
       </c>
       <c r="F41" s="7">
-        <f>1000/E41/1.757</f>
+        <f t="shared" si="0"/>
         <v>184.78959856307608</v>
       </c>
       <c r="G41" s="2">
-        <f>F41/D41</f>
+        <f t="shared" si="2"/>
         <v>0.76995666067948365</v>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
         <v>152</v>
       </c>
       <c r="G42" s="2">
-        <f>F42/D42</f>
+        <f t="shared" si="2"/>
         <v>1.0555555555555556</v>
       </c>
     </row>
@@ -1824,11 +1824,11 @@
         <v>3.77</v>
       </c>
       <c r="F43" s="7">
-        <f>1000/E43/1.757</f>
+        <f t="shared" ref="F43:F83" si="3">1000/E43/1.757</f>
         <v>150.96869060325579</v>
       </c>
       <c r="G43" s="2">
-        <f>F43/D43</f>
+        <f t="shared" si="2"/>
         <v>1.2580724216937982</v>
       </c>
     </row>
@@ -1849,11 +1849,11 @@
         <v>3.827</v>
       </c>
       <c r="F44" s="7">
-        <f>1000/E44/1.757</f>
+        <f t="shared" si="3"/>
         <v>148.72013681062825</v>
       </c>
       <c r="G44" s="2">
-        <f>F44/D44</f>
+        <f t="shared" si="2"/>
         <v>0.826222982281268</v>
       </c>
     </row>
@@ -1874,11 +1874,11 @@
         <v>4.1900000000000004</v>
       </c>
       <c r="F45" s="7">
-        <f>1000/E45/1.757</f>
+        <f t="shared" si="3"/>
         <v>135.83579082918243</v>
       </c>
       <c r="G45" s="2">
-        <f>F45/D45</f>
+        <f t="shared" si="2"/>
         <v>0.7717942660749002</v>
       </c>
     </row>
@@ -1899,11 +1899,11 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="F46" s="6">
-        <f>1000/E46/1.757</f>
+        <f t="shared" si="3"/>
         <v>129.35271899415326</v>
       </c>
       <c r="G46" s="2">
-        <f>F46/D46</f>
+        <f t="shared" si="2"/>
         <v>0.95112293378053869</v>
       </c>
     </row>
@@ -1924,11 +1924,11 @@
         <v>4.43</v>
       </c>
       <c r="F47" s="7">
-        <f>1000/E47/1.757</f>
+        <f t="shared" si="3"/>
         <v>128.4767412131545</v>
       </c>
       <c r="G47" s="2">
-        <f>F47/D47</f>
+        <f t="shared" si="2"/>
         <v>0.66914969381851297</v>
       </c>
     </row>
@@ -1949,11 +1949,11 @@
         <v>4.57</v>
       </c>
       <c r="F48" s="7">
-        <f>1000/E48/1.757</f>
+        <f t="shared" si="3"/>
         <v>124.54091106658082</v>
       </c>
       <c r="G48" s="2">
-        <f>F48/D48</f>
+        <f t="shared" si="2"/>
         <v>1.1531565839498223</v>
       </c>
     </row>
@@ -1974,11 +1974,11 @@
         <v>4.71</v>
       </c>
       <c r="F49" s="6">
-        <f>1000/E49/1.757</f>
+        <f t="shared" si="3"/>
         <v>120.83905808371006</v>
       </c>
       <c r="G49" s="2">
-        <f>F49/D49</f>
+        <f t="shared" si="2"/>
         <v>0.94405514127898482</v>
       </c>
     </row>
@@ -1999,11 +1999,11 @@
         <v>4.84</v>
       </c>
       <c r="F50" s="7">
-        <f>1000/E50/1.757</f>
+        <f t="shared" si="3"/>
         <v>117.5933809037757</v>
       </c>
       <c r="G50" s="2">
-        <f>F50/D50</f>
+        <f t="shared" si="2"/>
         <v>0.69996060061771248</v>
       </c>
     </row>
@@ -2024,11 +2024,11 @@
         <v>5.0199999999999996</v>
       </c>
       <c r="F51" s="7">
-        <f>1000/E51/1.757</f>
+        <f t="shared" si="3"/>
         <v>113.37688517415825</v>
       </c>
       <c r="G51" s="2">
-        <f>F51/D51</f>
+        <f t="shared" si="2"/>
         <v>0.59050461028207424</v>
       </c>
     </row>
@@ -2049,11 +2049,11 @@
         <v>5.05</v>
       </c>
       <c r="F52" s="6">
-        <f>1000/E52/1.757</f>
+        <f t="shared" si="3"/>
         <v>112.70335912361868</v>
       </c>
       <c r="G52" s="2">
-        <f>F52/D52</f>
+        <f t="shared" si="2"/>
         <v>0.78266221613624087</v>
       </c>
     </row>
@@ -2074,11 +2074,11 @@
         <v>5.21</v>
       </c>
       <c r="F53" s="7">
-        <f>1000/E53/1.757</f>
+        <f t="shared" si="3"/>
         <v>109.24221949602196</v>
       </c>
       <c r="G53" s="2">
-        <f>F53/D53</f>
+        <f t="shared" si="2"/>
         <v>1.3005026130478805</v>
       </c>
     </row>
@@ -2099,11 +2099,11 @@
         <v>5.32</v>
       </c>
       <c r="F54" s="6">
-        <f>1000/E54/1.757</f>
+        <f t="shared" si="3"/>
         <v>106.98345179967562</v>
       </c>
       <c r="G54" s="2">
-        <f>F54/D54</f>
+        <f t="shared" si="2"/>
         <v>1.3372931474959453</v>
       </c>
     </row>
@@ -2124,11 +2124,11 @@
         <v>5.57</v>
       </c>
       <c r="F55" s="6">
-        <f>1000/E55/1.757</f>
+        <f t="shared" si="3"/>
         <v>102.18168107258067</v>
       </c>
       <c r="G55" s="2">
-        <f>F55/D55</f>
+        <f t="shared" si="2"/>
         <v>0.75133589023956382</v>
       </c>
     </row>
@@ -2149,11 +2149,11 @@
         <v>6</v>
       </c>
       <c r="F56" s="7">
-        <f>1000/E56/1.757</f>
+        <f t="shared" si="3"/>
         <v>94.858660595712394</v>
       </c>
       <c r="G56" s="2">
-        <f>F56/D56</f>
+        <f t="shared" si="2"/>
         <v>0.87832093144178147</v>
       </c>
     </row>
@@ -2174,11 +2174,11 @@
         <v>6.38</v>
       </c>
       <c r="F57" s="6">
-        <f>1000/E57/1.757</f>
+        <f t="shared" si="3"/>
         <v>89.208771720105702</v>
       </c>
       <c r="G57" s="2">
-        <f>F57/D57</f>
+        <f t="shared" si="2"/>
         <v>1.1151096465013213</v>
       </c>
     </row>
@@ -2199,11 +2199,11 @@
         <v>6.69</v>
       </c>
       <c r="F58" s="7">
-        <f>1000/E58/1.757</f>
+        <f t="shared" si="3"/>
         <v>85.075031924405735</v>
       </c>
       <c r="G58" s="2">
-        <f>F58/D58</f>
+        <f t="shared" si="2"/>
         <v>0.5907988328083732</v>
       </c>
     </row>
@@ -2224,11 +2224,11 @@
         <v>7.54</v>
       </c>
       <c r="F59" s="7">
-        <f>1000/E59/1.757</f>
+        <f t="shared" si="3"/>
         <v>75.484345301627897</v>
       </c>
       <c r="G59" s="2">
-        <f>F59/D59</f>
+        <f t="shared" si="2"/>
         <v>1.0483936847448319</v>
       </c>
     </row>
@@ -2249,11 +2249,11 @@
         <v>8.11</v>
       </c>
       <c r="F60" s="7">
-        <f>1000/E60/1.757</f>
+        <f t="shared" si="3"/>
         <v>70.179033732956157</v>
       </c>
       <c r="G60" s="2">
-        <f>F60/D60</f>
+        <f t="shared" si="2"/>
         <v>0.58482528110796794</v>
       </c>
     </row>
@@ -2274,11 +2274,11 @@
         <v>8.49</v>
       </c>
       <c r="F61" s="6">
-        <f>1000/E61/1.757</f>
+        <f t="shared" si="3"/>
         <v>67.037922682482261</v>
       </c>
       <c r="G61" s="2">
-        <f>F61/D61</f>
+        <f t="shared" si="2"/>
         <v>0.93108225947892032</v>
       </c>
     </row>
@@ -2299,11 +2299,11 @@
         <v>8.7100000000000009</v>
       </c>
       <c r="F62" s="7">
-        <f>1000/E62/1.757</f>
+        <f t="shared" si="3"/>
         <v>65.344657126782351</v>
       </c>
       <c r="G62" s="2">
-        <f>F62/D62</f>
+        <f t="shared" si="2"/>
         <v>0.90756468231642151</v>
       </c>
     </row>
@@ -2324,11 +2324,11 @@
         <v>9.19</v>
       </c>
       <c r="F63" s="7">
-        <f>1000/E63/1.757</f>
+        <f t="shared" si="3"/>
         <v>61.931660889474905</v>
       </c>
       <c r="G63" s="2">
-        <f>F63/D63</f>
+        <f t="shared" si="2"/>
         <v>0.73728167725565363</v>
       </c>
     </row>
@@ -2349,11 +2349,11 @@
         <v>9.2799999999999994</v>
       </c>
       <c r="F64" s="6">
-        <f>1000/E64/1.757</f>
+        <f t="shared" si="3"/>
         <v>61.331030557572667</v>
       </c>
       <c r="G64" s="2">
-        <f>F64/D64</f>
+        <f t="shared" si="2"/>
         <v>0.76663788196965832</v>
       </c>
     </row>
@@ -2374,11 +2374,11 @@
         <v>9.41</v>
       </c>
       <c r="F65" s="8">
-        <f>1000/E65/1.757</f>
+        <f t="shared" si="3"/>
         <v>60.483736830422359</v>
       </c>
       <c r="G65" s="2">
-        <f>F65/D65</f>
+        <f t="shared" si="2"/>
         <v>0.42002595021126637</v>
       </c>
     </row>
@@ -2399,11 +2399,11 @@
         <v>9.49</v>
       </c>
       <c r="F66" s="6">
-        <f>1000/E66/1.757</f>
+        <f t="shared" si="3"/>
         <v>59.973863390334493</v>
       </c>
       <c r="G66" s="2">
-        <f>F66/D66</f>
+        <f t="shared" ref="G66:G97" si="4">F66/D66</f>
         <v>0.46854580773698823</v>
       </c>
     </row>
@@ -2424,11 +2424,11 @@
         <v>10.44</v>
       </c>
       <c r="F67" s="7">
-        <f>1000/E67/1.757</f>
+        <f t="shared" si="3"/>
         <v>54.516471606731265</v>
       </c>
       <c r="G67" s="2">
-        <f>F67/D67</f>
+        <f t="shared" si="4"/>
         <v>0.75717321676015648</v>
       </c>
     </row>
@@ -2449,11 +2449,11 @@
         <v>11.83</v>
       </c>
       <c r="F68" s="7">
-        <f>1000/E68/1.757</f>
+        <f t="shared" si="3"/>
         <v>48.110901401037566</v>
       </c>
       <c r="G68" s="2">
-        <f>F68/D68</f>
+        <f t="shared" si="4"/>
         <v>0.66820696390329948</v>
       </c>
     </row>
@@ -2474,11 +2474,11 @@
         <v>12.2</v>
       </c>
       <c r="F69" s="6">
-        <f>1000/E69/1.757</f>
+        <f t="shared" si="3"/>
         <v>46.651800292973313</v>
       </c>
       <c r="G69" s="2">
-        <f>F69/D69</f>
+        <f t="shared" si="4"/>
         <v>0.58314750366216639</v>
       </c>
     </row>
@@ -2499,11 +2499,11 @@
         <v>14.9</v>
       </c>
       <c r="F70" s="7">
-        <f>1000/E70/1.757</f>
+        <f t="shared" si="3"/>
         <v>38.198118360689556</v>
       </c>
       <c r="G70" s="2">
-        <f>F70/D70</f>
+        <f t="shared" si="4"/>
         <v>0.7957941325143657</v>
       </c>
     </row>
@@ -2524,11 +2524,11 @@
         <v>16.8</v>
       </c>
       <c r="F71" s="6">
-        <f>1000/E71/1.757</f>
+        <f t="shared" si="3"/>
         <v>33.878093069897282</v>
       </c>
       <c r="G71" s="2">
-        <f>F71/D71</f>
+        <f t="shared" si="4"/>
         <v>0.47052907041524006</v>
       </c>
     </row>
@@ -2549,11 +2549,11 @@
         <v>18.329999999999998</v>
       </c>
       <c r="F72" s="7">
-        <f>1000/E72/1.757</f>
+        <f t="shared" si="3"/>
         <v>31.050298067336303</v>
       </c>
       <c r="G72" s="2">
-        <f>F72/D72</f>
+        <f t="shared" si="4"/>
         <v>0.43125413982411531</v>
       </c>
     </row>
@@ -2574,11 +2574,11 @@
         <v>19.02</v>
       </c>
       <c r="F73" s="7">
-        <f>1000/E73/1.757</f>
+        <f t="shared" si="3"/>
         <v>29.923867695808326</v>
       </c>
       <c r="G73" s="2">
-        <f>F73/D73</f>
+        <f t="shared" si="4"/>
         <v>0.4156092735528934</v>
       </c>
     </row>
@@ -2599,11 +2599,11 @@
         <v>25.3</v>
       </c>
       <c r="F74" s="6">
-        <f>1000/E74/1.757</f>
+        <f t="shared" si="3"/>
         <v>22.496125042461436</v>
       </c>
       <c r="G74" s="2">
-        <f>F74/D74</f>
+        <f t="shared" si="4"/>
         <v>0.70300390757691988</v>
       </c>
     </row>
@@ -2624,11 +2624,11 @@
         <v>27.52</v>
       </c>
       <c r="F75" s="6">
-        <f>1000/E75/1.757</f>
+        <f t="shared" si="3"/>
         <v>20.681394025227995</v>
       </c>
       <c r="G75" s="2">
-        <f>F75/D75</f>
+        <f t="shared" si="4"/>
         <v>0.43086237552558321</v>
       </c>
     </row>
@@ -2649,11 +2649,11 @@
         <v>33</v>
       </c>
       <c r="F76" s="6">
-        <f>1000/E76/1.757</f>
+        <f t="shared" si="3"/>
         <v>17.247029199220435</v>
       </c>
       <c r="G76" s="2">
-        <f>F76/D76</f>
+        <f t="shared" si="4"/>
         <v>0.7186262166341848</v>
       </c>
     </row>
@@ -2674,11 +2674,11 @@
         <v>42.9</v>
       </c>
       <c r="F77" s="6">
-        <f>1000/E77/1.757</f>
+        <f t="shared" si="3"/>
         <v>13.266945537861874</v>
       </c>
       <c r="G77" s="2">
-        <f>F77/D77</f>
+        <f t="shared" si="4"/>
         <v>0.41459204805818356</v>
       </c>
     </row>
@@ -2699,11 +2699,11 @@
         <v>53.4</v>
       </c>
       <c r="F78" s="6">
-        <f>1000/E78/1.757</f>
+        <f t="shared" si="3"/>
         <v>10.65827647142836</v>
       </c>
       <c r="G78" s="2">
-        <f>F78/D78</f>
+        <f t="shared" si="4"/>
         <v>0.44409485297618168</v>
       </c>
     </row>
@@ -2724,11 +2724,11 @@
         <v>67</v>
       </c>
       <c r="F79" s="4">
-        <f>1000/E79/1.757</f>
+        <f t="shared" si="3"/>
         <v>8.4948054264817063</v>
       </c>
       <c r="G79" s="2">
-        <f>F79/D79</f>
+        <f t="shared" si="4"/>
         <v>0.53092533915510665</v>
       </c>
     </row>
@@ -2749,11 +2749,11 @@
         <v>71.900000000000006</v>
       </c>
       <c r="F80" s="4">
-        <f>1000/E80/1.757</f>
+        <f t="shared" si="3"/>
         <v>7.9158826644544416</v>
       </c>
       <c r="G80" s="2">
-        <f>F80/D80</f>
+        <f t="shared" si="4"/>
         <v>0.4947426665284026</v>
       </c>
     </row>
@@ -2774,11 +2774,11 @@
         <v>73.599999999999994</v>
       </c>
       <c r="F81" s="4">
-        <f>1000/E81/1.757</f>
+        <f t="shared" si="3"/>
         <v>7.7330429833461194</v>
       </c>
       <c r="G81" s="2">
-        <f>F81/D81</f>
+        <f t="shared" si="4"/>
         <v>0.12888404972243533</v>
       </c>
     </row>
@@ -2799,11 +2799,11 @@
         <v>74</v>
       </c>
       <c r="F82" s="4">
-        <f>1000/E82/1.757</f>
+        <f t="shared" si="3"/>
         <v>7.691242751003708</v>
       </c>
       <c r="G82" s="2">
-        <f>F82/D82</f>
+        <f t="shared" si="4"/>
         <v>0.48070267193773175</v>
       </c>
     </row>
@@ -2824,11 +2824,11 @@
         <v>78</v>
       </c>
       <c r="F83" s="4">
-        <f>1000/E83/1.757</f>
+        <f t="shared" si="3"/>
         <v>7.2968200458240311</v>
       </c>
       <c r="G83" s="2">
-        <f>F83/D83</f>
+        <f t="shared" si="4"/>
         <v>0.36484100229120153</v>
       </c>
     </row>
@@ -2895,11 +2895,11 @@
         <v>85.5</v>
       </c>
       <c r="F86" s="4">
-        <f>1000/E86/1.757</f>
+        <f t="shared" ref="F86:F91" si="5">1000/E86/1.757</f>
         <v>6.6567481119798169</v>
       </c>
       <c r="G86" s="2">
-        <f>F86/D86</f>
+        <f t="shared" ref="G86:G91" si="6">F86/D86</f>
         <v>0.11094580186633028</v>
       </c>
     </row>
@@ -2920,11 +2920,11 @@
         <v>93.5</v>
       </c>
       <c r="F87" s="4">
-        <f>1000/E87/1.757</f>
+        <f t="shared" si="5"/>
         <v>6.0871867761954475</v>
       </c>
       <c r="G87" s="2">
-        <f>F87/D87</f>
+        <f t="shared" si="6"/>
         <v>0.38044917351221547</v>
       </c>
     </row>
@@ -2945,11 +2945,11 @@
         <v>107.1</v>
       </c>
       <c r="F88" s="3">
-        <f>1000/E88/1.757</f>
+        <f t="shared" si="5"/>
         <v>5.314210677630947</v>
       </c>
       <c r="G88" s="2">
-        <f>F88/D88</f>
+        <f t="shared" si="6"/>
         <v>0.33213816735193419</v>
       </c>
       <c r="N88" s="2"/>
@@ -2973,11 +2973,11 @@
         <v>107.2</v>
       </c>
       <c r="F89" s="3">
-        <f>1000/E89/1.757</f>
+        <f t="shared" si="5"/>
         <v>5.3092533915510671</v>
       </c>
       <c r="G89" s="2">
-        <f>F89/D89</f>
+        <f t="shared" si="6"/>
         <v>0.3318283369719417</v>
       </c>
       <c r="N89" s="2"/>
@@ -3001,11 +3001,11 @@
         <v>108.1</v>
       </c>
       <c r="F90" s="3">
-        <f>1000/E90/1.757</f>
+        <f t="shared" si="5"/>
         <v>5.265050541852677</v>
       </c>
       <c r="G90" s="2">
-        <f>F90/D90</f>
+        <f t="shared" si="6"/>
         <v>0.32906565886579231</v>
       </c>
       <c r="N90" s="2"/>
@@ -3029,11 +3029,11 @@
         <v>121</v>
       </c>
       <c r="F91" s="3">
-        <f>1000/E91/1.757</f>
+        <f t="shared" si="5"/>
         <v>4.7037352361510276</v>
       </c>
       <c r="G91" s="2">
-        <f>F91/D91</f>
+        <f t="shared" si="6"/>
         <v>0.29398345225943923</v>
       </c>
       <c r="N91" s="2"/>

--- a/results.xlsx
+++ b/results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\__my_github\dhrystone_score\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A23F03E2-D764-4A3E-B2D5-18EBACB567C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{299C7A0F-7898-4AC3-AB78-E0530AC0E907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="840" yWindow="-108" windowWidth="29988" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="869" yWindow="-109" windowWidth="22425" windowHeight="13259" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="results" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="103">
   <si>
     <t>MCU</t>
   </si>
@@ -380,6 +380,18 @@
   </si>
   <si>
     <t>GD32H737VMT6(oc)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ESP8684</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Os</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>O3</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -436,7 +448,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -463,6 +475,7 @@
     <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -738,29 +751,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P96"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:P98"/>
+  <sheetFormatPr defaultColWidth="8.84375" defaultRowHeight="16.3" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="33.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.21875" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.5546875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.88671875" style="1"/>
-    <col min="10" max="10" width="33.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="3.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.23046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.4609375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.4609375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.23046875" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.4609375" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.07421875" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.53515625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.84375" style="1"/>
+    <col min="10" max="10" width="33.23046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.69140625" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="4.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.07421875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.3046875" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.88671875" style="1"/>
+    <col min="17" max="16384" width="8.84375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -783,7 +796,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -800,15 +813,15 @@
         <v>2.3400000000000001E-2</v>
       </c>
       <c r="F2" s="7">
-        <f t="shared" ref="F2:F41" si="0">1000/E2/1.757</f>
+        <f>1000/E2/1.757</f>
         <v>24322.733486080102</v>
       </c>
       <c r="G2" s="2">
-        <f t="shared" ref="G2:G33" si="1">F2/D2</f>
+        <f>F2/D2</f>
         <v>5.5914329853057705</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -825,15 +838,15 @@
         <v>0.05</v>
       </c>
       <c r="F3" s="7">
-        <f t="shared" si="0"/>
+        <f>1000/E3/1.757</f>
         <v>11383.039271485488</v>
       </c>
       <c r="G3" s="2">
-        <f t="shared" si="1"/>
+        <f>F3/D3</f>
         <v>2.6167906371231004</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>99</v>
       </c>
@@ -850,15 +863,15 @@
         <v>0.249</v>
       </c>
       <c r="F4" s="7">
-        <f t="shared" si="0"/>
+        <f>1000/E4/1.757</f>
         <v>2285.7508577280096</v>
       </c>
       <c r="G4" s="2">
-        <f t="shared" si="1"/>
+        <f>F4/D4</f>
         <v>2.2857508577280097</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -875,15 +888,15 @@
         <v>0.32900000000000001</v>
       </c>
       <c r="F5" s="6">
-        <f t="shared" si="0"/>
+        <f>1000/E5/1.757</f>
         <v>1729.9451780373081</v>
       </c>
       <c r="G5" s="2">
-        <f t="shared" si="1"/>
+        <f>F5/D5</f>
         <v>2.1624314725466349</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>65</v>
       </c>
@@ -900,15 +913,15 @@
         <v>0.40300000000000002</v>
       </c>
       <c r="F6" s="6">
-        <f t="shared" si="0"/>
+        <f>1000/E6/1.757</f>
         <v>1412.2877508046511</v>
       </c>
       <c r="G6" s="2">
-        <f t="shared" si="1"/>
+        <f>F6/D6</f>
         <v>2.9422661475096898</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
         <v>90</v>
       </c>
@@ -925,15 +938,15 @@
         <v>0.41499999999999998</v>
       </c>
       <c r="F7" s="7">
-        <f t="shared" si="0"/>
+        <f>1000/E7/1.757</f>
         <v>1371.4505146368058</v>
       </c>
       <c r="G7" s="2">
-        <f t="shared" si="1"/>
+        <f>F7/D7</f>
         <v>2.2857508577280097</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
         <v>99</v>
       </c>
@@ -950,15 +963,15 @@
         <v>0.42</v>
       </c>
       <c r="F8" s="7">
-        <f t="shared" si="0"/>
+        <f>1000/E8/1.757</f>
         <v>1355.1237227958916</v>
       </c>
       <c r="G8" s="2">
-        <f t="shared" si="1"/>
+        <f>F8/D8</f>
         <v>1.3551237227958917</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>65</v>
       </c>
@@ -975,15 +988,15 @@
         <v>0.61</v>
       </c>
       <c r="F9" s="6">
-        <f t="shared" si="0"/>
+        <f>1000/E9/1.757</f>
         <v>933.03600585946617</v>
       </c>
       <c r="G9" s="2">
-        <f t="shared" si="1"/>
+        <f>F9/D9</f>
         <v>1.9438250122072211</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -1000,15 +1013,15 @@
         <v>0.68300000000000005</v>
       </c>
       <c r="F10" s="6">
-        <f t="shared" si="0"/>
+        <f>1000/E10/1.757</f>
         <v>833.31180611167554</v>
       </c>
       <c r="G10" s="2">
-        <f t="shared" si="1"/>
+        <f>F10/D10</f>
         <v>1.0416397576395944</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
         <v>90</v>
       </c>
@@ -1025,15 +1038,15 @@
         <v>0.70099999999999996</v>
       </c>
       <c r="F11" s="7">
-        <f t="shared" si="0"/>
+        <f>1000/E11/1.757</f>
         <v>811.91435602606896</v>
       </c>
       <c r="G11" s="2">
-        <f t="shared" si="1"/>
+        <f>F11/D11</f>
         <v>1.3531905933767816</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
         <v>98</v>
       </c>
@@ -1050,15 +1063,15 @@
         <v>0.83199999999999996</v>
       </c>
       <c r="F12" s="7">
-        <f t="shared" si="0"/>
+        <f>1000/E12/1.757</f>
         <v>684.07687929600286</v>
       </c>
       <c r="G12" s="2">
-        <f t="shared" si="1"/>
+        <f>F12/D12</f>
         <v>1.5547201802181883</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>35</v>
       </c>
@@ -1075,15 +1088,15 @@
         <v>1.08</v>
       </c>
       <c r="F13" s="6">
-        <f t="shared" si="0"/>
+        <f>1000/E13/1.757</f>
         <v>526.99255886506887</v>
       </c>
       <c r="G13" s="2">
-        <f t="shared" si="1"/>
+        <f>F13/D13</f>
         <v>1.3174813971626722</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
         <v>76</v>
       </c>
@@ -1100,15 +1113,15 @@
         <v>1.1499999999999999</v>
       </c>
       <c r="F14" s="7">
-        <f t="shared" si="0"/>
+        <f>1000/E14/1.757</f>
         <v>494.91475093415164</v>
       </c>
       <c r="G14" s="2">
-        <f t="shared" si="1"/>
+        <f>F14/D14</f>
         <v>1.3448770405819339</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
         <v>43</v>
       </c>
@@ -1125,15 +1138,15 @@
         <v>1.21</v>
       </c>
       <c r="F15" s="7">
-        <f t="shared" si="0"/>
+        <f>1000/E15/1.757</f>
         <v>470.37352361510278</v>
       </c>
       <c r="G15" s="2">
-        <f t="shared" si="1"/>
+        <f>F15/D15</f>
         <v>1.3065931211530633</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
         <v>60</v>
       </c>
@@ -1150,15 +1163,15 @@
         <v>1.232</v>
       </c>
       <c r="F16" s="7">
-        <f t="shared" si="0"/>
+        <f>1000/E16/1.757</f>
         <v>461.97399640769027</v>
       </c>
       <c r="G16" s="2">
-        <f t="shared" si="1"/>
+        <f>F16/D16</f>
         <v>1.4436687387740321</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
         <v>10</v>
       </c>
@@ -1175,15 +1188,15 @@
         <v>1.4</v>
       </c>
       <c r="F17" s="7">
-        <f t="shared" si="0"/>
+        <f>1000/E17/1.757</f>
         <v>406.53711683876742</v>
       </c>
       <c r="G17" s="2">
-        <f t="shared" si="1"/>
+        <f>F17/D17</f>
         <v>1.4946217530837038</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
         <v>94</v>
       </c>
@@ -1200,15 +1213,15 @@
         <v>1.464</v>
       </c>
       <c r="F18" s="7">
-        <f t="shared" si="0"/>
+        <f>1000/E18/1.757</f>
         <v>388.76500244144421</v>
       </c>
       <c r="G18" s="2">
-        <f t="shared" si="1"/>
+        <f>F18/D18</f>
         <v>1.5550600097657767</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
         <v>98</v>
       </c>
@@ -1225,15 +1238,15 @@
         <v>1.4690000000000001</v>
       </c>
       <c r="F19" s="7">
-        <f t="shared" si="0"/>
+        <f>1000/E19/1.757</f>
         <v>387.44177234463876</v>
       </c>
       <c r="G19" s="2">
-        <f t="shared" si="1"/>
+        <f>F19/D19</f>
         <v>0.88054948260145172</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
         <v>39</v>
       </c>
@@ -1250,15 +1263,15 @@
         <v>1.49</v>
       </c>
       <c r="F20" s="7">
-        <f t="shared" si="0"/>
+        <f>1000/E20/1.757</f>
         <v>381.98118360689551</v>
       </c>
       <c r="G20" s="2">
-        <f t="shared" si="1"/>
+        <f>F20/D20</f>
         <v>1.9894853312859142</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
         <v>72</v>
       </c>
@@ -1275,15 +1288,15 @@
         <v>1.54</v>
       </c>
       <c r="F21" s="7">
-        <f t="shared" si="0"/>
+        <f>1000/E21/1.757</f>
         <v>369.57919712615217</v>
       </c>
       <c r="G21" s="2">
-        <f t="shared" si="1"/>
+        <f>F21/D21</f>
         <v>1.2832611011324728</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
         <v>12</v>
       </c>
@@ -1300,15 +1313,15 @@
         <v>1.59</v>
       </c>
       <c r="F22" s="7">
-        <f t="shared" si="0"/>
+        <f>1000/E22/1.757</f>
         <v>357.95720979514107</v>
       </c>
       <c r="G22" s="2">
-        <f t="shared" si="1"/>
+        <f>F22/D22</f>
         <v>1.4914883741464211</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
         <v>87</v>
       </c>
@@ -1325,15 +1338,15 @@
         <v>1.71</v>
       </c>
       <c r="F23" s="7">
-        <f t="shared" si="0"/>
+        <f>1000/E23/1.757</f>
         <v>332.83740559899087</v>
       </c>
       <c r="G23" s="2">
-        <f t="shared" si="1"/>
+        <f>F23/D23</f>
         <v>1.1556854361076072</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
         <v>13</v>
       </c>
@@ -1350,15 +1363,15 @@
         <v>1.76</v>
       </c>
       <c r="F24" s="7">
-        <f t="shared" si="0"/>
+        <f>1000/E24/1.757</f>
         <v>323.38179748538312</v>
       </c>
       <c r="G24" s="2">
-        <f t="shared" si="1"/>
+        <f>F24/D24</f>
         <v>1.1549349910192255</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
         <v>14</v>
       </c>
@@ -1375,15 +1388,15 @@
         <v>1.8</v>
       </c>
       <c r="F25" s="7">
-        <f t="shared" si="0"/>
+        <f>1000/E25/1.757</f>
         <v>316.19553531904131</v>
       </c>
       <c r="G25" s="2">
-        <f t="shared" si="1"/>
+        <f>F25/D25</f>
         <v>1.1292697689965761</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
         <v>42</v>
       </c>
@@ -1400,15 +1413,15 @@
         <v>1.8140000000000001</v>
       </c>
       <c r="F26" s="7">
-        <f t="shared" si="0"/>
+        <f>1000/E26/1.757</f>
         <v>313.7552169648701</v>
       </c>
       <c r="G26" s="2">
-        <f t="shared" si="1"/>
+        <f>F26/D26</f>
         <v>1.3073134040202921</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
         <v>83</v>
       </c>
@@ -1425,15 +1438,15 @@
         <v>1.85</v>
       </c>
       <c r="F27" s="7">
-        <f t="shared" si="0"/>
+        <f>1000/E27/1.757</f>
         <v>307.64971004014831</v>
       </c>
       <c r="G27" s="2">
-        <f t="shared" si="1"/>
+        <f>F27/D27</f>
         <v>1.47908514442379</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
         <v>84</v>
       </c>
@@ -1450,15 +1463,15 @@
         <v>2.06</v>
       </c>
       <c r="F28" s="7">
-        <f t="shared" si="0"/>
+        <f>1000/E28/1.757</f>
         <v>276.28736095838559</v>
       </c>
       <c r="G28" s="2">
-        <f t="shared" si="1"/>
+        <f>F28/D28</f>
         <v>1.1511973373266067</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
         <v>76</v>
       </c>
@@ -1475,15 +1488,15 @@
         <v>2.0699999999999998</v>
       </c>
       <c r="F29" s="7">
-        <f t="shared" si="0"/>
+        <f>1000/E29/1.757</f>
         <v>274.95263940786202</v>
       </c>
       <c r="G29" s="2">
-        <f t="shared" si="1"/>
+        <f>F29/D29</f>
         <v>0.74715391143440768</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>89</v>
       </c>
@@ -1500,15 +1513,15 @@
         <v>2.12</v>
       </c>
       <c r="F30" s="6">
-        <f t="shared" si="0"/>
+        <f>1000/E30/1.757</f>
         <v>268.46790734635579</v>
       </c>
       <c r="G30" s="2">
-        <f t="shared" si="1"/>
+        <f>F30/D30</f>
         <v>1.0487027630717023</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
         <v>15</v>
       </c>
@@ -1525,15 +1538,15 @@
         <v>2.15</v>
       </c>
       <c r="F31" s="7">
-        <f t="shared" si="0"/>
+        <f>1000/E31/1.757</f>
         <v>264.72184352291833</v>
       </c>
       <c r="G31" s="2">
-        <f t="shared" si="1"/>
+        <f>F31/D31</f>
         <v>1.5041013836529451</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>33</v>
       </c>
@@ -1550,15 +1563,15 @@
         <v>2.16</v>
       </c>
       <c r="F32" s="6">
-        <f t="shared" si="0"/>
+        <f>1000/E32/1.757</f>
         <v>263.49627943253444</v>
       </c>
       <c r="G32" s="2">
-        <f t="shared" si="1"/>
+        <f>F32/D32</f>
         <v>1.3174813971626722</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
         <v>41</v>
       </c>
@@ -1575,816 +1588,815 @@
         <v>2.1880000000000002</v>
       </c>
       <c r="F33" s="7">
-        <f t="shared" si="0"/>
+        <f>1000/E33/1.757</f>
         <v>260.12429779445807</v>
       </c>
       <c r="G33" s="2">
-        <f t="shared" si="1"/>
+        <f>F33/D33</f>
         <v>1.4451349877469892</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D34" s="1">
+        <v>120</v>
+      </c>
+      <c r="E34" s="9">
+        <v>2.444</v>
+      </c>
+      <c r="F34" s="10">
+        <f>1000/E34/1.757</f>
+        <v>232.87723550502227</v>
+      </c>
+      <c r="G34" s="2">
+        <f>F34/D34</f>
+        <v>1.940643629208519</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A35" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B35" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C35" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D34" s="1">
+      <c r="D35" s="1">
         <v>250</v>
       </c>
-      <c r="E34" s="9">
+      <c r="E35" s="9">
         <v>2.5870000000000002</v>
       </c>
-      <c r="F34" s="3">
-        <f t="shared" si="0"/>
-        <v>220.00462449720695</v>
-      </c>
-      <c r="G34" s="2">
-        <f t="shared" ref="G34:G65" si="2">F34/D34</f>
-        <v>0.88001849798882781</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A35" s="1" t="s">
+      <c r="F35" s="10">
+        <v>220</v>
+      </c>
+      <c r="G35" s="2">
+        <f>F35/D35</f>
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A36" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D35" s="1">
-        <v>168</v>
-      </c>
-      <c r="E35" s="9">
-        <v>2.59</v>
-      </c>
-      <c r="F35" s="7">
-        <f t="shared" si="0"/>
-        <v>219.74979288582023</v>
-      </c>
-      <c r="G35" s="2">
-        <f t="shared" si="2"/>
-        <v>1.3080344814632157</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A36" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D36" s="1">
+        <v>168</v>
+      </c>
+      <c r="E36" s="9">
+        <v>2.59</v>
+      </c>
+      <c r="F36" s="7">
+        <f>1000/E36/1.757</f>
+        <v>219.74979288582023</v>
+      </c>
+      <c r="G36" s="2">
+        <f>F36/D36</f>
+        <v>1.3080344814632157</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A37" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D36" s="1">
+      <c r="D37" s="1">
         <v>108</v>
       </c>
-      <c r="E36" s="9">
+      <c r="E37" s="9">
         <v>2.66</v>
       </c>
-      <c r="F36" s="7">
-        <f t="shared" si="0"/>
+      <c r="F37" s="7">
+        <f>1000/E37/1.757</f>
         <v>213.96690359935124</v>
       </c>
-      <c r="G36" s="2">
-        <f t="shared" si="2"/>
+      <c r="G37" s="2">
+        <f>F37/D37</f>
         <v>1.9811750333273264</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A37" s="1" t="s">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A38" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B38" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C38" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="D37" s="1">
+      <c r="D38" s="1">
         <v>144</v>
       </c>
-      <c r="E37" s="9">
+      <c r="E38" s="9">
         <v>2.69</v>
       </c>
-      <c r="F37" s="7">
-        <f t="shared" si="0"/>
+      <c r="F38" s="7">
+        <f>1000/E38/1.757</f>
         <v>211.58065560381945</v>
       </c>
-      <c r="G37" s="2">
-        <f t="shared" si="2"/>
+      <c r="G38" s="2">
+        <f>F38/D38</f>
         <v>1.4693101083598572</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A38" s="1" t="s">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A39" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B39" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C39" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D38" s="1">
+      <c r="D39" s="1">
         <v>288</v>
       </c>
-      <c r="E38" s="9">
+      <c r="E39" s="9">
         <v>2.79</v>
       </c>
-      <c r="F38" s="7">
-        <f t="shared" si="0"/>
+      <c r="F39" s="7">
+        <f>1000/E39/1.757</f>
         <v>203.99711956067179</v>
       </c>
-      <c r="G38" s="2">
-        <f t="shared" si="2"/>
+      <c r="G39" s="2">
+        <f>F39/D39</f>
         <v>0.7083233318078882</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A39" s="1" t="s">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A40" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B40" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C40" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D39" s="1">
+      <c r="D40" s="1">
         <v>192</v>
       </c>
-      <c r="E39" s="9">
+      <c r="E40" s="9">
         <v>2.82</v>
       </c>
-      <c r="F39" s="7">
-        <f t="shared" si="0"/>
+      <c r="F40" s="7">
+        <f>1000/E40/1.757</f>
         <v>201.82693743768596</v>
       </c>
-      <c r="G39" s="2">
-        <f t="shared" si="2"/>
+      <c r="G40" s="2">
+        <f>F40/D40</f>
         <v>1.0511819658212811</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A40" s="1" t="s">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A41" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B41" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D40" s="1">
-        <v>168</v>
-      </c>
-      <c r="E40" s="9">
-        <v>2.93</v>
-      </c>
-      <c r="F40" s="7">
-        <f t="shared" si="0"/>
-        <v>194.24981691954756</v>
-      </c>
-      <c r="G40" s="2">
-        <f t="shared" si="2"/>
-        <v>1.1562489102354021</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A41" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D41" s="1">
+        <v>168</v>
+      </c>
+      <c r="E41" s="9">
+        <v>2.93</v>
+      </c>
+      <c r="F41" s="7">
+        <f>1000/E41/1.757</f>
+        <v>194.24981691954756</v>
+      </c>
+      <c r="G41" s="2">
+        <f>F41/D41</f>
+        <v>1.1562489102354021</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A42" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D42" s="1">
         <v>240</v>
       </c>
-      <c r="E41" s="9">
+      <c r="E42" s="9">
         <v>3.08</v>
       </c>
-      <c r="F41" s="7">
-        <f t="shared" si="0"/>
+      <c r="F42" s="7">
+        <f>1000/E42/1.757</f>
         <v>184.78959856307608</v>
       </c>
-      <c r="G41" s="2">
-        <f t="shared" si="2"/>
+      <c r="G42" s="2">
+        <f>F42/D42</f>
         <v>0.76995666067948365</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D42" s="1">
-        <v>144</v>
-      </c>
-      <c r="E42" s="9">
-        <v>3.74</v>
-      </c>
-      <c r="F42" s="6">
-        <v>152</v>
-      </c>
-      <c r="G42" s="2">
-        <f t="shared" si="2"/>
-        <v>1.0555555555555556</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D43" s="1">
+        <v>144</v>
+      </c>
+      <c r="E43" s="9">
+        <v>3.74</v>
+      </c>
+      <c r="F43" s="6">
+        <v>152</v>
+      </c>
+      <c r="G43" s="2">
+        <f>F43/D43</f>
+        <v>1.0555555555555556</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A44" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C44" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D43" s="1">
+      <c r="D44" s="1">
         <v>120</v>
       </c>
-      <c r="E43" s="9">
+      <c r="E44" s="9">
         <v>3.77</v>
       </c>
-      <c r="F43" s="7">
-        <f t="shared" ref="F43:F83" si="3">1000/E43/1.757</f>
+      <c r="F44" s="7">
+        <f>1000/E44/1.757</f>
         <v>150.96869060325579</v>
       </c>
-      <c r="G43" s="2">
-        <f t="shared" si="2"/>
+      <c r="G44" s="2">
+        <f>F44/D44</f>
         <v>1.2580724216937982</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A44" s="1" t="s">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A45" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B45" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D44" s="1">
-        <v>180</v>
-      </c>
-      <c r="E44" s="9">
-        <v>3.827</v>
-      </c>
-      <c r="F44" s="7">
-        <f t="shared" si="3"/>
-        <v>148.72013681062825</v>
-      </c>
-      <c r="G44" s="2">
-        <f t="shared" si="2"/>
-        <v>0.826222982281268</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A45" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D45" s="1">
+        <v>180</v>
+      </c>
+      <c r="E45" s="9">
+        <v>3.827</v>
+      </c>
+      <c r="F45" s="7">
+        <f>1000/E45/1.757</f>
+        <v>148.72013681062825</v>
+      </c>
+      <c r="G45" s="2">
+        <f>F45/D45</f>
+        <v>0.826222982281268</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A46" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D46" s="1">
+        <v>120</v>
+      </c>
+      <c r="E46" s="9">
+        <v>3.91</v>
+      </c>
+      <c r="F46" s="10">
+        <f>1000/E46/1.757</f>
+        <v>145.56316203945636</v>
+      </c>
+      <c r="G46" s="2">
+        <f>F46/D46</f>
+        <v>1.213026350328803</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A47" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D47" s="1">
         <v>176</v>
       </c>
-      <c r="E45" s="9">
+      <c r="E47" s="9">
         <v>4.1900000000000004</v>
       </c>
-      <c r="F45" s="7">
-        <f t="shared" si="3"/>
+      <c r="F47" s="7">
+        <f>1000/E47/1.757</f>
         <v>135.83579082918243</v>
       </c>
-      <c r="G45" s="2">
-        <f t="shared" si="2"/>
+      <c r="G47" s="2">
+        <f>F47/D47</f>
         <v>0.7717942660749002</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D46" s="1">
-        <v>136</v>
-      </c>
-      <c r="E46" s="9">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="F46" s="6">
-        <f t="shared" si="3"/>
-        <v>129.35271899415326</v>
-      </c>
-      <c r="G46" s="2">
-        <f t="shared" si="2"/>
-        <v>0.95112293378053869</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A47" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D47" s="1">
-        <v>192</v>
-      </c>
-      <c r="E47" s="9">
-        <v>4.43</v>
-      </c>
-      <c r="F47" s="7">
-        <f t="shared" si="3"/>
-        <v>128.4767412131545</v>
-      </c>
-      <c r="G47" s="2">
-        <f t="shared" si="2"/>
-        <v>0.66914969381851297</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D48" s="1">
-        <v>108</v>
+        <v>136</v>
       </c>
       <c r="E48" s="9">
-        <v>4.57</v>
-      </c>
-      <c r="F48" s="7">
-        <f t="shared" si="3"/>
-        <v>124.54091106658082</v>
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="F48" s="6">
+        <f>1000/E48/1.757</f>
+        <v>129.35271899415326</v>
       </c>
       <c r="G48" s="2">
-        <f t="shared" si="2"/>
-        <v>1.1531565839498223</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+        <f>F48/D48</f>
+        <v>0.95112293378053869</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A49" s="1" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D49" s="1">
-        <v>128</v>
+        <v>192</v>
       </c>
       <c r="E49" s="9">
-        <v>4.71</v>
-      </c>
-      <c r="F49" s="6">
-        <f t="shared" si="3"/>
-        <v>120.83905808371006</v>
+        <v>4.43</v>
+      </c>
+      <c r="F49" s="7">
+        <f>1000/E49/1.757</f>
+        <v>128.4767412131545</v>
       </c>
       <c r="G49" s="2">
-        <f t="shared" si="2"/>
-        <v>0.94405514127898482</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+        <f>F49/D49</f>
+        <v>0.66914969381851297</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A50" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D50" s="1">
-        <v>168</v>
+        <v>108</v>
       </c>
       <c r="E50" s="9">
-        <v>4.84</v>
+        <v>4.57</v>
       </c>
       <c r="F50" s="7">
-        <f t="shared" si="3"/>
-        <v>117.5933809037757</v>
+        <f>1000/E50/1.757</f>
+        <v>124.54091106658082</v>
       </c>
       <c r="G50" s="2">
-        <f t="shared" si="2"/>
-        <v>0.69996060061771248</v>
+        <f>F50/D50</f>
+        <v>1.1531565839498223</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D51" s="1">
+        <v>128</v>
+      </c>
+      <c r="E51" s="9">
+        <v>4.71</v>
+      </c>
+      <c r="F51" s="6">
+        <f>1000/E51/1.757</f>
+        <v>120.83905808371006</v>
+      </c>
+      <c r="G51" s="2">
+        <f>F51/D51</f>
+        <v>0.94405514127898482</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A52" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D52" s="1">
+        <v>168</v>
+      </c>
+      <c r="E52" s="9">
+        <v>4.84</v>
+      </c>
+      <c r="F52" s="7">
+        <f>1000/E52/1.757</f>
+        <v>117.5933809037757</v>
+      </c>
+      <c r="G52" s="2">
+        <f>F52/D52</f>
+        <v>0.69996060061771248</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A53" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B53" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C53" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="D51" s="1">
+      <c r="D53" s="1">
         <v>192</v>
       </c>
-      <c r="E51" s="9">
+      <c r="E53" s="9">
         <v>5.0199999999999996</v>
       </c>
-      <c r="F51" s="7">
-        <f t="shared" si="3"/>
+      <c r="F53" s="7">
+        <f>1000/E53/1.757</f>
         <v>113.37688517415825</v>
       </c>
-      <c r="G51" s="2">
-        <f t="shared" si="2"/>
+      <c r="G53" s="2">
+        <f>F53/D53</f>
         <v>0.59050461028207424</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A54" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B54" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C54" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D52" s="1">
+      <c r="D54" s="1">
         <v>144</v>
       </c>
-      <c r="E52" s="9">
+      <c r="E54" s="9">
         <v>5.05</v>
       </c>
-      <c r="F52" s="6">
-        <f t="shared" si="3"/>
+      <c r="F54" s="6">
+        <f>1000/E54/1.757</f>
         <v>112.70335912361868</v>
       </c>
-      <c r="G52" s="2">
-        <f t="shared" si="2"/>
+      <c r="G54" s="2">
+        <f>F54/D54</f>
         <v>0.78266221613624087</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A53" s="1" t="s">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A55" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B55" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D53" s="1">
-        <v>84</v>
-      </c>
-      <c r="E53" s="9">
-        <v>5.21</v>
-      </c>
-      <c r="F53" s="7">
-        <f t="shared" si="3"/>
-        <v>109.24221949602196</v>
-      </c>
-      <c r="G53" s="2">
-        <f t="shared" si="2"/>
-        <v>1.3005026130478805</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D54" s="1">
-        <v>80</v>
-      </c>
-      <c r="E54" s="9">
-        <v>5.32</v>
-      </c>
-      <c r="F54" s="6">
-        <f t="shared" si="3"/>
-        <v>106.98345179967562</v>
-      </c>
-      <c r="G54" s="2">
-        <f t="shared" si="2"/>
-        <v>1.3372931474959453</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D55" s="1">
-        <v>136</v>
+        <v>84</v>
       </c>
       <c r="E55" s="9">
-        <v>5.57</v>
-      </c>
-      <c r="F55" s="6">
-        <f t="shared" si="3"/>
-        <v>102.18168107258067</v>
+        <v>5.21</v>
+      </c>
+      <c r="F55" s="7">
+        <f>1000/E55/1.757</f>
+        <v>109.24221949602196</v>
       </c>
       <c r="G55" s="2">
-        <f t="shared" si="2"/>
-        <v>0.75133589023956382</v>
+        <f>F55/D55</f>
+        <v>1.3005026130478805</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D56" s="1">
+        <v>80</v>
+      </c>
+      <c r="E56" s="9">
+        <v>5.32</v>
+      </c>
+      <c r="F56" s="6">
+        <f>1000/E56/1.757</f>
+        <v>106.98345179967562</v>
+      </c>
+      <c r="G56" s="2">
+        <f>F56/D56</f>
+        <v>1.3372931474959453</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A57" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D57" s="1">
+        <v>136</v>
+      </c>
+      <c r="E57" s="9">
+        <v>5.57</v>
+      </c>
+      <c r="F57" s="6">
+        <f>1000/E57/1.757</f>
+        <v>102.18168107258067</v>
+      </c>
+      <c r="G57" s="2">
+        <f>F57/D57</f>
+        <v>0.75133589023956382</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A58" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B58" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D56" s="1">
+      <c r="D58" s="1">
         <v>108</v>
       </c>
-      <c r="E56" s="9">
+      <c r="E58" s="9">
         <v>6</v>
       </c>
-      <c r="F56" s="7">
-        <f t="shared" si="3"/>
+      <c r="F58" s="7">
+        <f>1000/E58/1.757</f>
         <v>94.858660595712394</v>
       </c>
-      <c r="G56" s="2">
-        <f t="shared" si="2"/>
+      <c r="G58" s="2">
+        <f>F58/D58</f>
         <v>0.87832093144178147</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D57" s="1">
-        <v>80</v>
-      </c>
-      <c r="E57" s="9">
-        <v>6.38</v>
-      </c>
-      <c r="F57" s="6">
-        <f t="shared" si="3"/>
-        <v>89.208771720105702</v>
-      </c>
-      <c r="G57" s="2">
-        <f t="shared" si="2"/>
-        <v>1.1151096465013213</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A58" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D58" s="1">
-        <v>144</v>
-      </c>
-      <c r="E58" s="9">
-        <v>6.69</v>
-      </c>
-      <c r="F58" s="7">
-        <f t="shared" si="3"/>
-        <v>85.075031924405735</v>
-      </c>
-      <c r="G58" s="2">
-        <f t="shared" si="2"/>
-        <v>0.5907988328083732</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D59" s="1">
+        <v>80</v>
+      </c>
+      <c r="E59" s="9">
+        <v>6.38</v>
+      </c>
+      <c r="F59" s="6">
+        <f>1000/E59/1.757</f>
+        <v>89.208771720105702</v>
+      </c>
+      <c r="G59" s="2">
+        <f>F59/D59</f>
+        <v>1.1151096465013213</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A60" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D60" s="1">
+        <v>144</v>
+      </c>
+      <c r="E60" s="9">
+        <v>6.69</v>
+      </c>
+      <c r="F60" s="7">
+        <f>1000/E60/1.757</f>
+        <v>85.075031924405735</v>
+      </c>
+      <c r="G60" s="2">
+        <f>F60/D60</f>
+        <v>0.5907988328083732</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A61" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D59" s="1">
-        <v>72</v>
-      </c>
-      <c r="E59" s="9">
-        <v>7.54</v>
-      </c>
-      <c r="F59" s="7">
-        <f t="shared" si="3"/>
-        <v>75.484345301627897</v>
-      </c>
-      <c r="G59" s="2">
-        <f t="shared" si="2"/>
-        <v>1.0483936847448319</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A60" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D60" s="1">
-        <v>120</v>
-      </c>
-      <c r="E60" s="9">
-        <v>8.11</v>
-      </c>
-      <c r="F60" s="7">
-        <f t="shared" si="3"/>
-        <v>70.179033732956157</v>
-      </c>
-      <c r="G60" s="2">
-        <f t="shared" si="2"/>
-        <v>0.58482528110796794</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>77</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>34</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D61" s="1">
         <v>72</v>
       </c>
       <c r="E61" s="9">
-        <v>8.49</v>
-      </c>
-      <c r="F61" s="6">
-        <f t="shared" si="3"/>
-        <v>67.037922682482261</v>
+        <v>7.54</v>
+      </c>
+      <c r="F61" s="7">
+        <f>1000/E61/1.757</f>
+        <v>75.484345301627897</v>
       </c>
       <c r="G61" s="2">
-        <f t="shared" si="2"/>
-        <v>0.93108225947892032</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+        <f>F61/D61</f>
+        <v>1.0483936847448319</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A62" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D62" s="1">
-        <v>72</v>
+        <v>120</v>
       </c>
       <c r="E62" s="9">
-        <v>8.7100000000000009</v>
+        <v>8.11</v>
       </c>
       <c r="F62" s="7">
-        <f t="shared" si="3"/>
-        <v>65.344657126782351</v>
+        <f>1000/E62/1.757</f>
+        <v>70.179033732956157</v>
       </c>
       <c r="G62" s="2">
-        <f t="shared" si="2"/>
-        <v>0.90756468231642151</v>
+        <f>F62/D62</f>
+        <v>0.58482528110796794</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D63" s="1">
+        <v>72</v>
+      </c>
+      <c r="E63" s="9">
+        <v>8.49</v>
+      </c>
+      <c r="F63" s="6">
+        <f>1000/E63/1.757</f>
+        <v>67.037922682482261</v>
+      </c>
+      <c r="G63" s="2">
+        <f>F63/D63</f>
+        <v>0.93108225947892032</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A64" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D64" s="1">
+        <v>72</v>
+      </c>
+      <c r="E64" s="9">
+        <v>8.7100000000000009</v>
+      </c>
+      <c r="F64" s="7">
+        <f>1000/E64/1.757</f>
+        <v>65.344657126782351</v>
+      </c>
+      <c r="G64" s="2">
+        <f>F64/D64</f>
+        <v>0.90756468231642151</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A65" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D65" s="1">
         <v>84</v>
       </c>
-      <c r="E63" s="9">
+      <c r="E65" s="9">
         <v>9.19</v>
       </c>
-      <c r="F63" s="7">
-        <f t="shared" si="3"/>
+      <c r="F65" s="7">
+        <f>1000/E65/1.757</f>
         <v>61.931660889474905</v>
       </c>
-      <c r="G63" s="2">
-        <f t="shared" si="2"/>
+      <c r="G65" s="2">
+        <f>F65/D65</f>
         <v>0.73728167725565363</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A66" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D64" s="1">
-        <v>80</v>
-      </c>
-      <c r="E64" s="9">
-        <v>9.2799999999999994</v>
-      </c>
-      <c r="F64" s="6">
-        <f t="shared" si="3"/>
-        <v>61.331030557572667</v>
-      </c>
-      <c r="G64" s="2">
-        <f t="shared" si="2"/>
-        <v>0.76663788196965832</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D65" s="1">
-        <v>144</v>
-      </c>
-      <c r="E65" s="9">
-        <v>9.41</v>
-      </c>
-      <c r="F65" s="8">
-        <f t="shared" si="3"/>
-        <v>60.483736830422359</v>
-      </c>
-      <c r="G65" s="2">
-        <f t="shared" si="2"/>
-        <v>0.42002595021126637</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
-        <v>78</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>37</v>
@@ -2393,273 +2405,273 @@
         <v>49</v>
       </c>
       <c r="D66" s="1">
-        <v>128</v>
+        <v>80</v>
       </c>
       <c r="E66" s="9">
-        <v>9.49</v>
+        <v>9.2799999999999994</v>
       </c>
       <c r="F66" s="6">
-        <f t="shared" si="3"/>
-        <v>59.973863390334493</v>
+        <f>1000/E66/1.757</f>
+        <v>61.331030557572667</v>
       </c>
       <c r="G66" s="2">
-        <f t="shared" ref="G66:G97" si="4">F66/D66</f>
-        <v>0.46854580773698823</v>
+        <f>F66/D66</f>
+        <v>0.76663788196965832</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>7</v>
+        <v>70</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="D67" s="1">
-        <v>72</v>
+        <v>144</v>
       </c>
       <c r="E67" s="9">
-        <v>10.44</v>
-      </c>
-      <c r="F67" s="7">
-        <f t="shared" si="3"/>
-        <v>54.516471606731265</v>
+        <v>9.41</v>
+      </c>
+      <c r="F67" s="8">
+        <f>1000/E67/1.757</f>
+        <v>60.483736830422359</v>
       </c>
       <c r="G67" s="2">
-        <f t="shared" si="4"/>
-        <v>0.75717321676015648</v>
+        <f>F67/D67</f>
+        <v>0.42002595021126637</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C68" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D68" s="1">
+        <v>128</v>
+      </c>
+      <c r="E68" s="9">
+        <v>9.49</v>
+      </c>
+      <c r="F68" s="6">
+        <f>1000/E68/1.757</f>
+        <v>59.973863390334493</v>
+      </c>
+      <c r="G68" s="2">
+        <f>F68/D68</f>
+        <v>0.46854580773698823</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A69" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D69" s="1">
+        <v>72</v>
+      </c>
+      <c r="E69" s="9">
+        <v>10.44</v>
+      </c>
+      <c r="F69" s="7">
+        <f>1000/E69/1.757</f>
+        <v>54.516471606731265</v>
+      </c>
+      <c r="G69" s="2">
+        <f>F69/D69</f>
+        <v>0.75717321676015648</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A70" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C70" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D68" s="1">
+      <c r="D70" s="1">
         <v>72</v>
       </c>
-      <c r="E68" s="9">
+      <c r="E70" s="9">
         <v>11.83</v>
       </c>
-      <c r="F68" s="7">
-        <f t="shared" si="3"/>
+      <c r="F70" s="7">
+        <f>1000/E70/1.757</f>
         <v>48.110901401037566</v>
       </c>
-      <c r="G68" s="2">
-        <f t="shared" si="4"/>
+      <c r="G70" s="2">
+        <f>F70/D70</f>
         <v>0.66820696390329948</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A71" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B71" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="C71" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D69" s="1">
+      <c r="D71" s="1">
         <v>80</v>
       </c>
-      <c r="E69" s="9">
+      <c r="E71" s="9">
         <v>12.2</v>
       </c>
-      <c r="F69" s="6">
-        <f t="shared" si="3"/>
+      <c r="F71" s="6">
+        <f>1000/E71/1.757</f>
         <v>46.651800292973313</v>
       </c>
-      <c r="G69" s="2">
-        <f t="shared" si="4"/>
+      <c r="G71" s="2">
+        <f>F71/D71</f>
         <v>0.58314750366216639</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A70" s="1" t="s">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A72" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B72" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="C72" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D70" s="1">
+      <c r="D72" s="1">
         <v>48</v>
       </c>
-      <c r="E70" s="9">
+      <c r="E72" s="9">
         <v>14.9</v>
       </c>
-      <c r="F70" s="7">
-        <f t="shared" si="3"/>
+      <c r="F72" s="7">
+        <f>1000/E72/1.757</f>
         <v>38.198118360689556</v>
       </c>
-      <c r="G70" s="2">
-        <f t="shared" si="4"/>
+      <c r="G72" s="2">
+        <f>F72/D72</f>
         <v>0.7957941325143657</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D71" s="1">
-        <v>72</v>
-      </c>
-      <c r="E71" s="9">
-        <v>16.8</v>
-      </c>
-      <c r="F71" s="6">
-        <f t="shared" si="3"/>
-        <v>33.878093069897282</v>
-      </c>
-      <c r="G71" s="2">
-        <f t="shared" si="4"/>
-        <v>0.47052907041524006</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A72" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D72" s="1">
-        <v>72</v>
-      </c>
-      <c r="E72" s="9">
-        <v>18.329999999999998</v>
-      </c>
-      <c r="F72" s="7">
-        <f t="shared" si="3"/>
-        <v>31.050298067336303</v>
-      </c>
-      <c r="G72" s="2">
-        <f t="shared" si="4"/>
-        <v>0.43125413982411531</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
-        <v>23</v>
+        <v>77</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D73" s="1">
         <v>72</v>
       </c>
       <c r="E73" s="9">
-        <v>19.02</v>
-      </c>
-      <c r="F73" s="7">
-        <f t="shared" si="3"/>
-        <v>29.923867695808326</v>
+        <v>16.8</v>
+      </c>
+      <c r="F73" s="6">
+        <f>1000/E73/1.757</f>
+        <v>33.878093069897282</v>
       </c>
       <c r="G73" s="2">
-        <f t="shared" si="4"/>
-        <v>0.4156092735528934</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+        <f>F73/D73</f>
+        <v>0.47052907041524006</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A74" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D74" s="1">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="E74" s="9">
-        <v>25.3</v>
-      </c>
-      <c r="F74" s="6">
-        <f t="shared" si="3"/>
-        <v>22.496125042461436</v>
+        <v>18.329999999999998</v>
+      </c>
+      <c r="F74" s="7">
+        <f>1000/E74/1.757</f>
+        <v>31.050298067336303</v>
       </c>
       <c r="G74" s="2">
-        <f t="shared" si="4"/>
-        <v>0.70300390757691988</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+        <f>F74/D74</f>
+        <v>0.43125413982411531</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A75" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D75" s="1">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="E75" s="9">
-        <v>27.52</v>
-      </c>
-      <c r="F75" s="6">
-        <f t="shared" si="3"/>
-        <v>20.681394025227995</v>
+        <v>19.02</v>
+      </c>
+      <c r="F75" s="7">
+        <f>1000/E75/1.757</f>
+        <v>29.923867695808326</v>
       </c>
       <c r="G75" s="2">
-        <f t="shared" si="4"/>
-        <v>0.43086237552558321</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+        <f>F75/D75</f>
+        <v>0.4156092735528934</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="D76" s="1">
+        <v>32</v>
+      </c>
+      <c r="E76" s="9">
+        <v>25.3</v>
+      </c>
+      <c r="F76" s="6">
+        <f>1000/E76/1.757</f>
+        <v>22.496125042461436</v>
+      </c>
+      <c r="G76" s="2">
+        <f>F76/D76</f>
+        <v>0.70300390757691988</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A77" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="E76" s="9">
-        <v>33</v>
-      </c>
-      <c r="F76" s="6">
-        <f t="shared" si="3"/>
-        <v>17.247029199220435</v>
-      </c>
-      <c r="G76" s="2">
-        <f t="shared" si="4"/>
-        <v>0.7186262166341848</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>8</v>
@@ -2668,26 +2680,26 @@
         <v>55</v>
       </c>
       <c r="D77" s="1">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="E77" s="9">
-        <v>42.9</v>
+        <v>27.52</v>
       </c>
       <c r="F77" s="6">
-        <f t="shared" si="3"/>
-        <v>13.266945537861874</v>
+        <f>1000/E77/1.757</f>
+        <v>20.681394025227995</v>
       </c>
       <c r="G77" s="2">
-        <f t="shared" si="4"/>
-        <v>0.41459204805818356</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+        <f>F77/D77</f>
+        <v>0.43086237552558321</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
         <v>61</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>62</v>
@@ -2696,118 +2708,118 @@
         <v>24</v>
       </c>
       <c r="E78" s="9">
+        <v>33</v>
+      </c>
+      <c r="F78" s="6">
+        <f>1000/E78/1.757</f>
+        <v>17.247029199220435</v>
+      </c>
+      <c r="G78" s="2">
+        <f>F78/D78</f>
+        <v>0.7186262166341848</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A79" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D79" s="1">
+        <v>32</v>
+      </c>
+      <c r="E79" s="9">
+        <v>42.9</v>
+      </c>
+      <c r="F79" s="6">
+        <f>1000/E79/1.757</f>
+        <v>13.266945537861874</v>
+      </c>
+      <c r="G79" s="2">
+        <f>F79/D79</f>
+        <v>0.41459204805818356</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A80" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D80" s="1">
+        <v>24</v>
+      </c>
+      <c r="E80" s="9">
         <v>53.4</v>
       </c>
-      <c r="F78" s="6">
-        <f t="shared" si="3"/>
+      <c r="F80" s="6">
+        <f>1000/E80/1.757</f>
         <v>10.65827647142836</v>
       </c>
-      <c r="G78" s="2">
-        <f t="shared" si="4"/>
+      <c r="G80" s="2">
+        <f>F80/D80</f>
         <v>0.44409485297618168</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A81" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D79" s="1">
-        <v>16</v>
-      </c>
-      <c r="E79" s="9">
-        <v>67</v>
-      </c>
-      <c r="F79" s="4">
-        <f t="shared" si="3"/>
-        <v>8.4948054264817063</v>
-      </c>
-      <c r="G79" s="2">
-        <f t="shared" si="4"/>
-        <v>0.53092533915510665</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D80" s="1">
-        <v>16</v>
-      </c>
-      <c r="E80" s="9">
-        <v>71.900000000000006</v>
-      </c>
-      <c r="F80" s="4">
-        <f t="shared" si="3"/>
-        <v>7.9158826644544416</v>
-      </c>
-      <c r="G80" s="2">
-        <f t="shared" si="4"/>
-        <v>0.4947426665284026</v>
-      </c>
-    </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A81" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D81" s="1">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="E81" s="9">
-        <v>73.599999999999994</v>
+        <v>67</v>
       </c>
       <c r="F81" s="4">
-        <f t="shared" si="3"/>
-        <v>7.7330429833461194</v>
+        <f>1000/E81/1.757</f>
+        <v>8.4948054264817063</v>
       </c>
       <c r="G81" s="2">
-        <f t="shared" si="4"/>
-        <v>0.12888404972243533</v>
-      </c>
-    </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+        <f>F81/D81</f>
+        <v>0.53092533915510665</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D82" s="6">
+      <c r="D82" s="1">
         <v>16</v>
       </c>
       <c r="E82" s="9">
-        <v>74</v>
+        <v>71.900000000000006</v>
       </c>
       <c r="F82" s="4">
-        <f t="shared" si="3"/>
-        <v>7.691242751003708</v>
+        <f>1000/E82/1.757</f>
+        <v>7.9158826644544416</v>
       </c>
       <c r="G82" s="2">
-        <f t="shared" si="4"/>
-        <v>0.48070267193773175</v>
-      </c>
-    </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+        <f>F82/D82</f>
+        <v>0.4947426665284026</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
         <v>44</v>
       </c>
@@ -2817,47 +2829,49 @@
       <c r="C83" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D83" s="6">
-        <v>20</v>
+      <c r="D83" s="1">
+        <v>60</v>
       </c>
       <c r="E83" s="9">
-        <v>78</v>
+        <v>73.599999999999994</v>
       </c>
       <c r="F83" s="4">
-        <f t="shared" si="3"/>
-        <v>7.2968200458240311</v>
+        <f>1000/E83/1.757</f>
+        <v>7.7330429833461194</v>
       </c>
       <c r="G83" s="2">
-        <f t="shared" si="4"/>
-        <v>0.36484100229120153</v>
-      </c>
-    </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+        <f>F83/D83</f>
+        <v>0.12888404972243533</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
-        <v>71</v>
+        <v>26</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D84" s="6">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="E84" s="9">
-        <v>79.099999999999994</v>
+        <v>74</v>
       </c>
       <c r="F84" s="4">
-        <v>7.2</v>
-      </c>
-      <c r="G84" s="1">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1000/E84/1.757</f>
+        <v>7.691242751003708</v>
+      </c>
+      <c r="G84" s="2">
+        <f>F84/D84</f>
+        <v>0.48070267193773175</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>7</v>
@@ -2869,21 +2883,23 @@
         <v>20</v>
       </c>
       <c r="E85" s="9">
-        <v>82.4</v>
+        <v>78</v>
       </c>
       <c r="F85" s="4">
-        <v>6.9</v>
-      </c>
-      <c r="G85" s="1">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
+        <f>1000/E85/1.757</f>
+        <v>7.2968200458240311</v>
+      </c>
+      <c r="G85" s="2">
+        <f>F85/D85</f>
+        <v>0.36484100229120153</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>51</v>
@@ -2892,65 +2908,61 @@
         <v>60</v>
       </c>
       <c r="E86" s="9">
-        <v>85.5</v>
+        <v>79.099999999999994</v>
       </c>
       <c r="F86" s="4">
-        <f t="shared" ref="F86:F91" si="5">1000/E86/1.757</f>
-        <v>6.6567481119798169</v>
-      </c>
-      <c r="G86" s="2">
-        <f t="shared" ref="G86:G91" si="6">F86/D86</f>
-        <v>0.11094580186633028</v>
-      </c>
-    </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
+        <v>7.2</v>
+      </c>
+      <c r="G86" s="1">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D87" s="6">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E87" s="9">
-        <v>93.5</v>
+        <v>82.4</v>
       </c>
       <c r="F87" s="4">
-        <f t="shared" si="5"/>
-        <v>6.0871867761954475</v>
-      </c>
-      <c r="G87" s="2">
-        <f t="shared" si="6"/>
-        <v>0.38044917351221547</v>
+        <v>6.9</v>
+      </c>
+      <c r="G87" s="1">
+        <v>0.35</v>
       </c>
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D88" s="6">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="E88" s="9">
-        <v>107.1</v>
-      </c>
-      <c r="F88" s="3">
-        <f t="shared" si="5"/>
-        <v>5.314210677630947</v>
+        <v>85.5</v>
+      </c>
+      <c r="F88" s="4">
+        <f>1000/E88/1.757</f>
+        <v>6.6567481119798169</v>
       </c>
       <c r="G88" s="2">
-        <f t="shared" si="6"/>
-        <v>0.33213816735193419</v>
+        <f>F88/D88</f>
+        <v>0.11094580186633028</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -2958,38 +2970,38 @@
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D89" s="6">
         <v>16</v>
       </c>
       <c r="E89" s="9">
-        <v>107.2</v>
-      </c>
-      <c r="F89" s="3">
-        <f t="shared" si="5"/>
-        <v>5.3092533915510671</v>
+        <v>93.5</v>
+      </c>
+      <c r="F89" s="4">
+        <f>1000/E89/1.757</f>
+        <v>6.0871867761954475</v>
       </c>
       <c r="G89" s="2">
-        <f t="shared" si="6"/>
-        <v>0.3318283369719417</v>
+        <f>F89/D89</f>
+        <v>0.38044917351221547</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" s="2"/>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A90" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>57</v>
@@ -2998,26 +3010,26 @@
         <v>16</v>
       </c>
       <c r="E90" s="9">
-        <v>108.1</v>
+        <v>107.1</v>
       </c>
       <c r="F90" s="3">
-        <f t="shared" si="5"/>
-        <v>5.265050541852677</v>
+        <f>1000/E90/1.757</f>
+        <v>5.314210677630947</v>
       </c>
       <c r="G90" s="2">
-        <f t="shared" si="6"/>
-        <v>0.32906565886579231</v>
+        <f>F90/D90</f>
+        <v>0.33213816735193419</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
       <c r="P90" s="2"/>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A91" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>57</v>
@@ -3026,122 +3038,122 @@
         <v>16</v>
       </c>
       <c r="E91" s="9">
-        <v>121</v>
+        <v>107.2</v>
       </c>
       <c r="F91" s="3">
-        <f t="shared" si="5"/>
-        <v>4.7037352361510276</v>
+        <f>1000/E91/1.757</f>
+        <v>5.3092533915510671</v>
       </c>
       <c r="G91" s="2">
-        <f t="shared" si="6"/>
-        <v>0.29398345225943923</v>
+        <f>F91/D91</f>
+        <v>0.3318283369719417</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
       <c r="P91" s="2"/>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A92" s="1" t="s">
-        <v>71</v>
+        <v>29</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D92" s="6">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E92" s="9">
-        <v>124.8</v>
-      </c>
-      <c r="F92" s="4">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="G92" s="1">
-        <v>0.23</v>
+        <v>108.1</v>
+      </c>
+      <c r="F92" s="3">
+        <f>1000/E92/1.757</f>
+        <v>5.265050541852677</v>
+      </c>
+      <c r="G92" s="2">
+        <f>F92/D92</f>
+        <v>0.32906565886579231</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
       <c r="P92" s="2"/>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A93" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D93" s="6">
+        <v>16</v>
+      </c>
+      <c r="E93" s="9">
+        <v>121</v>
+      </c>
+      <c r="F93" s="3">
+        <f>1000/E93/1.757</f>
+        <v>4.7037352361510276</v>
+      </c>
+      <c r="G93" s="2">
+        <f>F93/D93</f>
+        <v>0.29398345225943923</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A94" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="B94" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="C94" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D93" s="6">
-        <v>60</v>
-      </c>
-      <c r="E93" s="9">
-        <v>124.6</v>
-      </c>
-      <c r="F93" s="4">
+      <c r="D94" s="6">
+        <v>20</v>
+      </c>
+      <c r="E94" s="9">
+        <v>124.8</v>
+      </c>
+      <c r="F94" s="4">
         <v>4.5999999999999996</v>
       </c>
-      <c r="G93" s="1">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A94" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C94" s="5">
-        <v>8051</v>
-      </c>
-      <c r="D94" s="6">
-        <v>24</v>
-      </c>
-      <c r="E94" s="9">
-        <v>254</v>
-      </c>
-      <c r="F94" s="4">
-        <f>1000/E94/1.757</f>
-        <v>2.2407557621034426</v>
-      </c>
-      <c r="G94" s="2">
-        <f>F94/D94</f>
-        <v>9.3364823420976781E-2</v>
+      <c r="G94" s="1">
+        <v>0.23</v>
       </c>
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
-        <v>32</v>
+        <v>71</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C95" s="5">
-        <v>8051</v>
-      </c>
-      <c r="D95" s="1">
-        <v>16</v>
+        <v>8</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D95" s="6">
+        <v>60</v>
       </c>
       <c r="E95" s="9">
-        <v>883</v>
-      </c>
-      <c r="F95" s="3">
-        <f>1000/E95/1.757</f>
-        <v>0.64456621016339111</v>
-      </c>
-      <c r="G95" s="2">
-        <f>F95/D95</f>
-        <v>4.0285388135211944E-2</v>
+        <v>124.6</v>
+      </c>
+      <c r="F95" s="4">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G95" s="1">
+        <v>0.08</v>
       </c>
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>58</v>
@@ -3149,24 +3161,74 @@
       <c r="C96" s="5">
         <v>8051</v>
       </c>
-      <c r="D96" s="1">
-        <v>16</v>
+      <c r="D96" s="6">
+        <v>24</v>
       </c>
       <c r="E96" s="9">
-        <v>884</v>
-      </c>
-      <c r="F96" s="3">
+        <v>254</v>
+      </c>
+      <c r="F96" s="4">
         <f>1000/E96/1.757</f>
-        <v>0.64383706286682618</v>
+        <v>2.2407557621034426</v>
       </c>
       <c r="G96" s="2">
         <f>F96/D96</f>
+        <v>9.3364823420976781E-2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A97" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C97" s="5">
+        <v>8051</v>
+      </c>
+      <c r="D97" s="1">
+        <v>16</v>
+      </c>
+      <c r="E97" s="9">
+        <v>883</v>
+      </c>
+      <c r="F97" s="3">
+        <f>1000/E97/1.757</f>
+        <v>0.64456621016339111</v>
+      </c>
+      <c r="G97" s="2">
+        <f>F97/D97</f>
+        <v>4.0285388135211944E-2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A98" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C98" s="5">
+        <v>8051</v>
+      </c>
+      <c r="D98" s="1">
+        <v>16</v>
+      </c>
+      <c r="E98" s="9">
+        <v>884</v>
+      </c>
+      <c r="F98" s="3">
+        <f>1000/E98/1.757</f>
+        <v>0.64383706286682618</v>
+      </c>
+      <c r="G98" s="2">
+        <f>F98/D98</f>
         <v>4.0239816429176636E-2</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H42" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H96">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H98">
       <sortCondition descending="1" ref="F1:F42"/>
     </sortState>
   </autoFilter>

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\__my_github\dhrystone_score\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{299C7A0F-7898-4AC3-AB78-E0530AC0E907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{511EE673-ECB7-44A3-8246-F8D3FDBC9B70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="869" yWindow="-109" windowWidth="22425" windowHeight="13259" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
